--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_17sep26_Thurs.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_17sep26_Thurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BEB6DB-FF53-44B3-92AB-BEBBFAC8A51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89F6FE4-9B10-427E-B1A7-45524D9F4232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3453" uniqueCount="308">
   <si>
     <t>Date</t>
   </si>
@@ -1121,7 +1121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1276,17 +1276,8 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1685,7 +1676,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B2, $C$2:$C$747, C2, $D$2:$D$747, D2, $E$2:$E$747, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$747, B2, $C$2:$C$747, C2, $D$2:$D$747, D2, $E$2:$E$747, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -1722,7 +1713,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B3, $C$2:$C$747, C3, $D$2:$D$747, D3, $E$2:$E$747, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1759,7 +1750,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B4, $C$2:$C$747, C4, $D$2:$D$747, D4, $E$2:$E$747, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1796,7 +1787,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B5, $C$2:$C$747, C5, $D$2:$D$747, D5, $E$2:$E$747, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1833,7 +1824,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B6, $C$2:$C$747, C6, $D$2:$D$747, D6, $E$2:$E$747, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1870,7 +1861,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B7, $C$2:$C$747, C7, $D$2:$D$747, D7, $E$2:$E$747, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1909,7 +1900,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B8, $C$2:$C$747, C8, $D$2:$D$747, D8, $E$2:$E$747, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1955,7 +1946,7 @@
         <v>10880</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B9, $C$2:$C$747, C9, $D$2:$D$747, D9, $E$2:$E$747, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -1994,7 +1985,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B10, $C$2:$C$747, C10, $D$2:$D$747, D10, $E$2:$E$747, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2040,7 +2031,7 @@
         <v>10680</v>
       </c>
       <c r="N11" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B11, $C$2:$C$747, C11, $D$2:$D$747, D11, $E$2:$E$747, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
@@ -2079,7 +2070,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B12, $C$2:$C$747, C12, $D$2:$D$747, D12, $E$2:$E$747, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2116,7 +2107,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B13, $C$2:$C$747, C13, $D$2:$D$747, D13, $E$2:$E$747, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2155,7 +2146,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B14, $C$2:$C$747, C14, $D$2:$D$747, D14, $E$2:$E$747, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2192,7 +2183,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B15, $C$2:$C$747, C15, $D$2:$D$747, D15, $E$2:$E$747, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2229,7 +2220,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B16, $C$2:$C$747, C16, $D$2:$D$747, D16, $E$2:$E$747, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2266,7 +2257,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B17, $C$2:$C$747, C17, $D$2:$D$747, D17, $E$2:$E$747, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2307,7 +2298,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B18, $C$2:$C$747, C18, $D$2:$D$747, D18, $E$2:$E$747, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2346,7 +2337,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B19, $C$2:$C$747, C19, $D$2:$D$747, D19, $E$2:$E$747, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2383,7 +2374,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B20, $C$2:$C$747, C20, $D$2:$D$747, D20, $E$2:$E$747, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2420,7 +2411,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B21, $C$2:$C$747, C21, $D$2:$D$747, D21, $E$2:$E$747, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2457,7 +2448,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B22, $C$2:$C$747, C22, $D$2:$D$747, D22, $E$2:$E$747, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2504,7 +2495,7 @@
         <v>540</v>
       </c>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B23, $C$2:$C$747, C23, $D$2:$D$747, D23, $E$2:$E$747, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2543,7 +2534,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B24, $C$2:$C$747, C24, $D$2:$D$747, D24, $E$2:$E$747, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2580,7 +2571,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B25, $C$2:$C$747, C25, $D$2:$D$747, D25, $E$2:$E$747, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2626,7 +2617,7 @@
         <v>300</v>
       </c>
       <c r="N26" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B26, $C$2:$C$747, C26, $D$2:$D$747, D26, $E$2:$E$747, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -2665,7 +2656,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B27, $C$2:$C$747, C27, $D$2:$D$747, D27, $E$2:$E$747, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27"/>
@@ -2706,7 +2697,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B28, $C$2:$C$747, C28, $D$2:$D$747, D28, $E$2:$E$747, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -2747,7 +2738,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B29, $C$2:$C$747, C29, $D$2:$D$747, D29, $E$2:$E$747, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -2788,7 +2779,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B30, $C$2:$C$747, C30, $D$2:$D$747, D30, $E$2:$E$747, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -2829,7 +2820,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B31, $C$2:$C$747, C31, $D$2:$D$747, D31, $E$2:$E$747, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -2868,7 +2859,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B32, $C$2:$C$747, C32, $D$2:$D$747, D32, $E$2:$E$747, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -2909,7 +2900,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B33, $C$2:$C$747, C33, $D$2:$D$747, D33, $E$2:$E$747, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -2950,7 +2941,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B34, $C$2:$C$747, C34, $D$2:$D$747, D34, $E$2:$E$747, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34" s="30"/>
@@ -2989,7 +2980,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B35, $C$2:$C$747, C35, $D$2:$D$747, D35, $E$2:$E$747, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -3029,7 +3020,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B36, $C$2:$C$747, C36, $D$2:$D$747, D36, $E$2:$E$747, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -3070,7 +3061,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B37, $C$2:$C$747, C37, $D$2:$D$747, D37, $E$2:$E$747, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -3111,7 +3102,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B38, $C$2:$C$747, C38, $D$2:$D$747, D38, $E$2:$E$747, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -3150,7 +3141,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B39, $C$2:$C$747, C39, $D$2:$D$747, D39, $E$2:$E$747, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -3191,7 +3182,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B40, $C$2:$C$747, C40, $D$2:$D$747, D40, $E$2:$E$747, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -3230,7 +3221,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B41, $C$2:$C$747, C41, $D$2:$D$747, D41, $E$2:$E$747, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -3271,7 +3262,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B42, $C$2:$C$747, C42, $D$2:$D$747, D42, $E$2:$E$747, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -3312,7 +3303,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B43, $C$2:$C$747, C43, $D$2:$D$747, D43, $E$2:$E$747, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P43"/>
@@ -3359,7 +3350,7 @@
         <v>525</v>
       </c>
       <c r="N44" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B44, $C$2:$C$747, C44, $D$2:$D$747, D44, $E$2:$E$747, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3398,7 +3389,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B45, $C$2:$C$747, C45, $D$2:$D$747, D45, $E$2:$E$747, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -3446,7 +3437,7 @@
         <v>300</v>
       </c>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B46, $C$2:$C$747, C46, $D$2:$D$747, D46, $E$2:$E$747, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3485,7 +3476,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B47, $C$2:$C$747, C47, $D$2:$D$747, D47, $E$2:$E$747, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3522,7 +3513,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B48, $C$2:$C$747, C48, $D$2:$D$747, D48, $E$2:$E$747, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -3562,7 +3553,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B49, $C$2:$C$747, C49, $D$2:$D$747, D49, $E$2:$E$747, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3608,7 +3599,7 @@
         <v>720</v>
       </c>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B50, $C$2:$C$747, C50, $D$2:$D$747, D50, $E$2:$E$747, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3647,7 +3638,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B51, $C$2:$C$747, C51, $D$2:$D$747, D51, $E$2:$E$747, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="10"/>
@@ -3695,7 +3686,7 @@
         <v>300</v>
       </c>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B52, $C$2:$C$747, C52, $D$2:$D$747, D52, $E$2:$E$747, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -3741,7 +3732,7 @@
         <v>300</v>
       </c>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B53, $C$2:$C$747, C53, $D$2:$D$747, D53, $E$2:$E$747, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -3787,7 +3778,7 @@
         <v>500</v>
       </c>
       <c r="N54" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B54, $C$2:$C$747, C54, $D$2:$D$747, D54, $E$2:$E$747, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54" s="10"/>
@@ -3835,7 +3826,7 @@
         <v>460</v>
       </c>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B55, $C$2:$C$747, C55, $D$2:$D$747, D55, $E$2:$E$747, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -3882,7 +3873,7 @@
         <v>300</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B56, $C$2:$C$747, C56, $D$2:$D$747, D56, $E$2:$E$747, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P56" s="25"/>
@@ -3920,7 +3911,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B57, $C$2:$C$747, C57, $D$2:$D$747, D57, $E$2:$E$747, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3957,7 +3948,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B58, $C$2:$C$747, C58, $D$2:$D$747, D58, $E$2:$E$747, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -3996,7 +3987,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B59, $C$2:$C$747, C59, $D$2:$D$747, D59, $E$2:$E$747, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4036,7 +4027,7 @@
         <v>3156</v>
       </c>
       <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B60, $C$2:$C$747, C60, $D$2:$D$747, D60, $E$2:$E$747, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P60" s="19"/>
@@ -4074,7 +4065,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B61, $C$2:$C$747, C61, $D$2:$D$747, D61, $E$2:$E$747, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="19"/>
@@ -4112,13 +4103,13 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B62, $C$2:$C$747, C62, $D$2:$D$747, D62, $E$2:$E$747, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="26"/>
       <c r="P62" s="10"/>
     </row>
-    <row r="63" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3">
         <v>46304.375</v>
       </c>
@@ -4160,7 +4151,7 @@
         <v>26810</v>
       </c>
       <c r="N63" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B63, $C$2:$C$747, C63, $D$2:$D$747, D63, $E$2:$E$747, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4199,13 +4190,13 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B64, $C$2:$C$747, C64, $D$2:$D$747, D64, $E$2:$E$747, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
     </row>
-    <row r="65" spans="1:16" s="31" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" s="31" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -4247,7 +4238,7 @@
         <v>300</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B65, $C$2:$C$747, C65, $D$2:$D$747, D65, $E$2:$E$747, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65" s="10"/>
@@ -4288,11 +4279,11 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B66, $C$2:$C$747, C66, $D$2:$D$747, D66, $E$2:$E$747, E66) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$747, B66, $C$2:$C$747, C66, $D$2:$D$747, D66, $E$2:$E$747, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3">
         <v>46280.587500000001</v>
       </c>
@@ -4330,15 +4321,15 @@
         <v>17404</v>
       </c>
       <c r="M67" s="18">
-        <f>ABS((D67*E67)-L67)</f>
+        <f t="shared" ref="M67:M72" si="2">ABS((D67*E67)-L67)</f>
         <v>516</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B67, $C$2:$C$747, C67, $D$2:$D$747, D67, $E$2:$E$747, E67) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="3">
         <v>46304.375</v>
       </c>
@@ -4376,11 +4367,11 @@
         <v>35880</v>
       </c>
       <c r="M68" s="18">
-        <f>ABS((D68*E68)-L68)</f>
+        <f t="shared" si="2"/>
         <v>26710</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B68, $C$2:$C$747, C68, $D$2:$D$747, D68, $E$2:$E$747, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="41" t="s">
@@ -4425,15 +4416,15 @@
         <v>56375</v>
       </c>
       <c r="M69" s="18">
-        <f>ABS((D69*E69)-L69)</f>
+        <f t="shared" si="2"/>
         <v>34175</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B69, $C$2:$C$747, C69, $D$2:$D$747, D69, $E$2:$E$747, E69) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="3">
         <v>46275.375</v>
       </c>
@@ -4471,17 +4462,17 @@
         <v>10400</v>
       </c>
       <c r="M70" s="18">
-        <f>ABS((D70*E70)-L70)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B70, $C$2:$C$747, C70, $D$2:$D$747, D70, $E$2:$E$747, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70" s="10"/>
       <c r="P70" s="10"/>
     </row>
-    <row r="71" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="32">
         <v>46262.375</v>
       </c>
@@ -4509,7 +4500,7 @@
       <c r="I71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J71" s="57" t="s">
+      <c r="J71" s="29" t="s">
         <v>118</v>
       </c>
       <c r="K71" s="29" t="s">
@@ -4519,18 +4510,18 @@
         <v>3560</v>
       </c>
       <c r="M71" s="29">
-        <f>ABS((D71*E71)-L71)</f>
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="N71" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B71, $C$2:$C$747, C71, $D$2:$D$747, D71, $E$2:$E$747, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O71" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="72" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -4558,7 +4549,7 @@
       <c r="I72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="57" t="s">
+      <c r="J72" s="29" t="s">
         <v>118</v>
       </c>
       <c r="K72" s="29" t="s">
@@ -4568,11 +4559,11 @@
         <v>3510</v>
       </c>
       <c r="M72" s="29">
-        <f>ABS((D72*E72)-L72)</f>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N72" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B72, $C$2:$C$747, C72, $D$2:$D$747, D72, $E$2:$E$747, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O72" s="41" t="s">
@@ -4608,18 +4599,18 @@
       <c r="I73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J73" s="56" t="s">
+      <c r="J73" s="52" t="s">
         <v>55</v>
       </c>
       <c r="K73" s="17"/>
       <c r="L73" s="17"/>
       <c r="M73" s="17"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B73, $C$2:$C$747, C73, $D$2:$D$747, D73, $E$2:$E$747, E73) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
         <v>46276.375</v>
       </c>
@@ -4647,7 +4638,7 @@
       <c r="I74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J74" s="54" t="s">
+      <c r="J74" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K74" s="18" t="s">
@@ -4661,13 +4652,13 @@
         <v>646</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B74, $C$2:$C$747, C74, $D$2:$D$747, D74, $E$2:$E$747, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="10"/>
       <c r="P74" s="10"/>
     </row>
-    <row r="75" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
         <v>46304.375</v>
       </c>
@@ -4695,7 +4686,7 @@
       <c r="I75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J75" s="54" t="s">
+      <c r="J75" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K75" s="18" t="s">
@@ -4709,13 +4700,13 @@
         <v>26610</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B75, $C$2:$C$747, C75, $D$2:$D$747, D75, $E$2:$E$747, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="10"/>
       <c r="P75" s="10"/>
     </row>
-    <row r="76" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3">
         <v>46281.376388888886</v>
       </c>
@@ -4757,13 +4748,13 @@
         <v>300</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B76, $C$2:$C$747, C76, $D$2:$D$747, D76, $E$2:$E$747, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="10"/>
       <c r="P76" s="10"/>
     </row>
-    <row r="77" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -4805,7 +4796,7 @@
         <v>18850</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B77, $C$2:$C$747, C77, $D$2:$D$747, D77, $E$2:$E$747, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="10"/>
@@ -4839,19 +4830,19 @@
       <c r="I78" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J78" s="56" t="s">
+      <c r="J78" s="52" t="s">
         <v>41</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B78, $C$2:$C$747, C78, $D$2:$D$747, D78, $E$2:$E$747, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P78" s="26"/>
     </row>
-    <row r="79" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -4893,7 +4884,7 @@
         <v>650</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B79, $C$2:$C$747, C79, $D$2:$D$747, D79, $E$2:$E$747, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="10"/>
@@ -4927,20 +4918,20 @@
       <c r="I80" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="56" t="s">
+      <c r="J80" s="52" t="s">
         <v>55</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B80, $C$2:$C$747, C80, $D$2:$D$747, D80, $E$2:$E$747, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="10"/>
       <c r="P80" s="10"/>
     </row>
-    <row r="81" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3">
         <v>46267.375</v>
       </c>
@@ -4978,11 +4969,11 @@
         <v>8220</v>
       </c>
       <c r="M81" s="18">
-        <f>ABS((D81*E81)-L81)</f>
+        <f t="shared" ref="M81:M90" si="3">ABS((D81*E81)-L81)</f>
         <v>360</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B81, $C$2:$C$747, C81, $D$2:$D$747, D81, $E$2:$E$747, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="41" t="s">
@@ -4990,7 +4981,7 @@
       </c>
       <c r="P81" s="10"/>
     </row>
-    <row r="82" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="11">
         <v>46273.375</v>
       </c>
@@ -5028,17 +5019,17 @@
         <v>9170</v>
       </c>
       <c r="M82" s="29">
-        <f>ABS((D82*E82)-L82)</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B82, $C$2:$C$747, C82, $D$2:$D$747, D82, $E$2:$E$747, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O82" s="10"/>
       <c r="P82" s="10"/>
     </row>
-    <row r="83" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="32">
         <v>46269.542361111111</v>
       </c>
@@ -5076,19 +5067,17 @@
         <v>16219.999999999998</v>
       </c>
       <c r="M83" s="29">
-        <f>ABS((D83*E83)-L83)</f>
+        <f t="shared" si="3"/>
         <v>300.00000000000182</v>
       </c>
       <c r="N83" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B83, $C$2:$C$747, C83, $D$2:$D$747, D83, $E$2:$E$747, E83) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O83" s="41" t="s">
-        <v>247</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O83" s="54"/>
       <c r="P83" s="31"/>
     </row>
-    <row r="84" spans="1:16" s="19" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:16" s="19" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="32">
         <v>46272.530555555553</v>
       </c>
@@ -5126,19 +5115,17 @@
         <v>6334</v>
       </c>
       <c r="M84" s="29">
-        <f>ABS((D84*E84)-L84)</f>
+        <f t="shared" si="3"/>
         <v>274</v>
       </c>
       <c r="N84" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B84, $C$2:$C$747, C84, $D$2:$D$747, D84, $E$2:$E$747, E84) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O84" s="41" t="s">
-        <v>247</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O84" s="54"/>
       <c r="P84" s="31"/>
     </row>
-    <row r="85" spans="1:16" s="26" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
         <v>46276.375</v>
       </c>
@@ -5176,17 +5163,17 @@
         <v>8700</v>
       </c>
       <c r="M85" s="18">
-        <f>ABS((D85*E85)-L85)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B85, $C$2:$C$747, C85, $D$2:$D$747, D85, $E$2:$E$747, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="10"/>
       <c r="P85" s="10"/>
     </row>
-    <row r="86" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3">
         <v>46275.375</v>
       </c>
@@ -5224,15 +5211,15 @@
         <v>35880</v>
       </c>
       <c r="M86" s="18">
-        <f>ABS((D86*E86)-L86)</f>
+        <f t="shared" si="3"/>
         <v>26460</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B86, $C$2:$C$747, C86, $D$2:$D$747, D86, $E$2:$E$747, E86) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="43">
         <v>46273.375</v>
       </c>
@@ -5270,11 +5257,11 @@
         <v>19730.5</v>
       </c>
       <c r="M87" s="29">
-        <f>ABS((D87*E87)-L87)</f>
+        <f t="shared" si="3"/>
         <v>504.5</v>
       </c>
       <c r="N87" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B87, $C$2:$C$747, C87, $D$2:$D$747, D87, $E$2:$E$747, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O87" s="41" t="s">
@@ -5282,7 +5269,7 @@
       </c>
       <c r="P87" s="31"/>
     </row>
-    <row r="88" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="32">
         <v>46274.375</v>
       </c>
@@ -5320,11 +5307,11 @@
         <v>19690</v>
       </c>
       <c r="M88" s="29">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" si="3"/>
         <v>545</v>
       </c>
       <c r="N88" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B88, $C$2:$C$747, C88, $D$2:$D$747, D88, $E$2:$E$747, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O88" s="41" t="s">
@@ -5332,7 +5319,7 @@
       </c>
       <c r="P88" s="31"/>
     </row>
-    <row r="89" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
         <v>46275.375</v>
       </c>
@@ -5370,15 +5357,15 @@
         <v>3300</v>
       </c>
       <c r="M89" s="18">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B89, $C$2:$C$747, C89, $D$2:$D$747, D89, $E$2:$E$747, E89) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -5416,18 +5403,18 @@
         <v>8480</v>
       </c>
       <c r="M90" s="27">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="3"/>
         <v>280</v>
       </c>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B90, $C$2:$C$747, C90, $D$2:$D$747, D90, $E$2:$E$747, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="91" spans="1:16" s="25" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="8" t="s">
         <v>62</v>
       </c>
@@ -5460,13 +5447,13 @@
       <c r="L91" s="18"/>
       <c r="M91" s="18"/>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B91, $C$2:$C$747, C91, $D$2:$D$747, D91, $E$2:$E$747, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="10"/>
       <c r="P91" s="10"/>
     </row>
-    <row r="92" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="11">
         <v>46273.375</v>
       </c>
@@ -5508,11 +5495,11 @@
         <v>300</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B92, $C$2:$C$747, C92, $D$2:$D$747, D92, $E$2:$E$747, E92) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3">
         <v>46280.57708333333</v>
       </c>
@@ -5554,11 +5541,11 @@
         <v>300.75</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B93, $C$2:$C$747, C93, $D$2:$D$747, D93, $E$2:$E$747, E93) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" s="26" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3">
         <v>46268.375</v>
       </c>
@@ -5600,13 +5587,13 @@
         <v>1200</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B94, $C$2:$C$747, C94, $D$2:$D$747, D94, $E$2:$E$747, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="10"/>
       <c r="P94" s="10"/>
     </row>
-    <row r="95" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3">
         <v>46261.375</v>
       </c>
@@ -5648,12 +5635,12 @@
         <v>300</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B95, $C$2:$C$747, C95, $D$2:$D$747, D95, $E$2:$E$747, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95"/>
     </row>
-    <row r="96" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3">
         <v>46281.37777777778</v>
       </c>
@@ -5695,7 +5682,7 @@
         <v>810</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B96, $C$2:$C$747, C96, $D$2:$D$747, D96, $E$2:$E$747, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5727,20 +5714,20 @@
       <c r="I97" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J97" s="56" t="s">
+      <c r="J97" s="52" t="s">
         <v>41</v>
       </c>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
       <c r="M97" s="17"/>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B97, $C$2:$C$747, C97, $D$2:$D$747, D97, $E$2:$E$747, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="10"/>
       <c r="P97" s="25"/>
     </row>
-    <row r="98" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3">
         <v>46262.375</v>
       </c>
@@ -5778,17 +5765,17 @@
         <v>8420</v>
       </c>
       <c r="M98" s="18">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" ref="M98:M103" si="4">ABS((D98*E98)-L98)</f>
         <v>300</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B98, $C$2:$C$747, C98, $D$2:$D$747, D98, $E$2:$E$747, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="10"/>
       <c r="P98" s="10"/>
     </row>
-    <row r="99" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
         <v>46276.375</v>
       </c>
@@ -5826,15 +5813,15 @@
         <v>11320</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="4"/>
         <v>400</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B99, $C$2:$C$747, C99, $D$2:$D$747, D99, $E$2:$E$747, E99) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -5872,16 +5859,16 @@
         <v>20010</v>
       </c>
       <c r="M100" s="18">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="N100" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B100, $C$2:$C$747, C100, $D$2:$D$747, D100, $E$2:$E$747, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P100"/>
     </row>
-    <row r="101" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -5919,18 +5906,18 @@
         <v>15075</v>
       </c>
       <c r="M101" s="18">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="4"/>
         <v>645</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B101, $C$2:$C$747, C101, $D$2:$D$747, D101, $E$2:$E$747, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
         <v>46281.375</v>
       </c>
@@ -5968,15 +5955,15 @@
         <v>19300</v>
       </c>
       <c r="M102" s="18">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B102, $C$2:$C$747, C102, $D$2:$D$747, D102, $E$2:$E$747, E102) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -6014,15 +6001,15 @@
         <v>39300</v>
       </c>
       <c r="M103" s="18">
-        <f>ABS((D103*E103)-L103)</f>
+        <f t="shared" si="4"/>
         <v>18350</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B103, $C$2:$C$747, C103, $D$2:$D$747, D103, $E$2:$E$747, E103) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="8" t="s">
         <v>62</v>
       </c>
@@ -6054,11 +6041,11 @@
         <v>118</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B104, $C$2:$C$747, C104, $D$2:$D$747, D104, $E$2:$E$747, E104) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46281.375</v>
       </c>
@@ -6096,15 +6083,15 @@
         <v>16500</v>
       </c>
       <c r="M105" s="18">
-        <f>ABS((D105*E105)-L105)</f>
+        <f t="shared" ref="M105:M112" si="5">ABS((D105*E105)-L105)</f>
         <v>1400</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B105, $C$2:$C$747, C105, $D$2:$D$747, D105, $E$2:$E$747, E105) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
         <v>46267.375</v>
       </c>
@@ -6142,16 +6129,16 @@
         <v>9270</v>
       </c>
       <c r="M106" s="18">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B106, $C$2:$C$747, C106, $D$2:$D$747, D106, $E$2:$E$747, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P106" s="19"/>
     </row>
-    <row r="107" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -6189,17 +6176,17 @@
         <v>20260</v>
       </c>
       <c r="M107" s="18">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N107" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B107, $C$2:$C$747, C107, $D$2:$D$747, D107, $E$2:$E$747, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107"/>
       <c r="P107" s="31"/>
     </row>
-    <row r="108" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="45">
         <v>46273.385416666664</v>
       </c>
@@ -6237,11 +6224,11 @@
         <v>16580</v>
       </c>
       <c r="M108" s="47">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" si="5"/>
         <v>750</v>
       </c>
       <c r="N108" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B108, $C$2:$C$747, C108, $D$2:$D$747, D108, $E$2:$E$747, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108" s="25"/>
@@ -6249,7 +6236,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="109" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="11">
         <v>46243.375</v>
       </c>
@@ -6287,11 +6274,11 @@
         <v>8570</v>
       </c>
       <c r="M109" s="29">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B109, $C$2:$C$747, C109, $D$2:$D$747, D109, $E$2:$E$747, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="41" t="s">
@@ -6299,7 +6286,7 @@
       </c>
       <c r="P109" s="10"/>
     </row>
-    <row r="110" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="32">
         <v>46281.443055555559</v>
       </c>
@@ -6337,17 +6324,17 @@
         <v>5585</v>
       </c>
       <c r="M110" s="29">
-        <f>ABS((D110*E110)-L110)</f>
+        <f t="shared" si="5"/>
         <v>395</v>
       </c>
       <c r="N110" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B110, $C$2:$C$747, C110, $D$2:$D$747, D110, $E$2:$E$747, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O110" s="31"/>
       <c r="P110" s="31"/>
     </row>
-    <row r="111" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="32">
         <v>46281.388888888891</v>
       </c>
@@ -6385,17 +6372,17 @@
         <v>5730</v>
       </c>
       <c r="M111" s="29">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" si="5"/>
         <v>250</v>
       </c>
       <c r="N111" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B111, $C$2:$C$747, C111, $D$2:$D$747, D111, $E$2:$E$747, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O111" s="31"/>
       <c r="P111" s="31"/>
     </row>
-    <row r="112" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>46267.375</v>
       </c>
@@ -6433,16 +6420,16 @@
         <v>3005</v>
       </c>
       <c r="M112" s="18">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="5"/>
         <v>240</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B112, $C$2:$C$747, C112, $D$2:$D$747, D112, $E$2:$E$747, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P112" s="26"/>
     </row>
-    <row r="113" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6472,11 +6459,11 @@
       </c>
       <c r="J113" s="36"/>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B113, $C$2:$C$747, C113, $D$2:$D$747, D113, $E$2:$E$747, E113) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -6508,7 +6495,7 @@
         <v>118</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B114, $C$2:$C$747, C114, $D$2:$D$747, D114, $E$2:$E$747, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O114" s="41" t="s">
@@ -6516,7 +6503,7 @@
       </c>
       <c r="P114"/>
     </row>
-    <row r="115" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="32">
         <v>46267.461111111108</v>
       </c>
@@ -6530,7 +6517,7 @@
         <v>100</v>
       </c>
       <c r="E115" s="34">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F115" s="4">
         <v>7.2784810130000004</v>
@@ -6555,15 +6542,15 @@
       </c>
       <c r="M115" s="29">
         <f>ABS((D115*E115)-L115)</f>
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="N115" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B115, $C$2:$C$747, C115, $D$2:$D$747, D115, $E$2:$E$747, E115) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
       </c>
       <c r="O115" s="26"/>
     </row>
-    <row r="116" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="32">
         <v>46267.38958333333</v>
       </c>
@@ -6605,13 +6592,13 @@
         <v>700</v>
       </c>
       <c r="N116" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B116, $C$2:$C$747, C116, $D$2:$D$747, D116, $E$2:$E$747, E116) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
     </row>
-    <row r="117" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46266.375</v>
       </c>
@@ -6653,12 +6640,12 @@
         <v>300</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B117, $C$2:$C$747, C117, $D$2:$D$747, D117, $E$2:$E$747, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="10"/>
     </row>
-    <row r="118" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6693,13 +6680,13 @@
       <c r="L118" s="18"/>
       <c r="M118" s="18"/>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B118, $C$2:$C$747, C118, $D$2:$D$747, D118, $E$2:$E$747, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="10"/>
       <c r="P118" s="10"/>
     </row>
-    <row r="119" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6729,7 +6716,7 @@
       </c>
       <c r="J119" s="36"/>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B119, $C$2:$C$747, C119, $D$2:$D$747, D119, $E$2:$E$747, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="41" t="s">
@@ -6737,7 +6724,7 @@
       </c>
       <c r="P119"/>
     </row>
-    <row r="120" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3">
         <v>46267.375</v>
       </c>
@@ -6775,15 +6762,15 @@
         <v>16755</v>
       </c>
       <c r="M120" s="18">
-        <f>ABS((D120*E120)-L120)</f>
+        <f t="shared" ref="M120:M127" si="6">ABS((D120*E120)-L120)</f>
         <v>295</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B120, $C$2:$C$747, C120, $D$2:$D$747, D120, $E$2:$E$747, E120) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="32">
         <v>46267.375</v>
       </c>
@@ -6821,18 +6808,18 @@
         <v>5755</v>
       </c>
       <c r="M121" s="29">
-        <f>ABS((D121*E121)-L121)</f>
+        <f t="shared" si="6"/>
         <v>275</v>
       </c>
       <c r="N121" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B121, $C$2:$C$747, C121, $D$2:$D$747, D121, $E$2:$E$747, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O121" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="32">
         <v>46267.375</v>
       </c>
@@ -6870,18 +6857,18 @@
         <v>5805</v>
       </c>
       <c r="M122" s="29">
-        <f>ABS((D122*E122)-L122)</f>
+        <f t="shared" si="6"/>
         <v>225</v>
       </c>
       <c r="N122" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B122, $C$2:$C$747, C122, $D$2:$D$747, D122, $E$2:$E$747, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O122" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
         <v>46274.375</v>
       </c>
@@ -6919,15 +6906,15 @@
         <v>3400</v>
       </c>
       <c r="M123" s="18">
-        <f>ABS((D123*E123)-L123)</f>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B123, $C$2:$C$747, C123, $D$2:$D$747, D123, $E$2:$E$747, E123) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3">
         <v>46274.375</v>
       </c>
@@ -6965,15 +6952,15 @@
         <v>4852</v>
       </c>
       <c r="M124" s="18">
-        <f>ABS((D124*E124)-L124)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B124, $C$2:$C$747, C124, $D$2:$D$747, D124, $E$2:$E$747, E124) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3">
         <v>46267.375</v>
       </c>
@@ -7011,15 +6998,15 @@
         <v>4080</v>
       </c>
       <c r="M125" s="18">
-        <f>ABS((D125*E125)-L125)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B125, $C$2:$C$747, C125, $D$2:$D$747, D125, $E$2:$E$747, E125) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7057,18 +7044,18 @@
         <v>17040</v>
       </c>
       <c r="M126" s="18">
-        <f>ABS((D126*E126)-L126)</f>
+        <f t="shared" si="6"/>
         <v>880</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B126, $C$2:$C$747, C126, $D$2:$D$747, D126, $E$2:$E$747, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3">
         <v>46274.375</v>
       </c>
@@ -7106,18 +7093,18 @@
         <v>11660</v>
       </c>
       <c r="M127" s="18">
-        <f>ABS((D127*E127)-L127)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B127, $C$2:$C$747, C127, $D$2:$D$747, D127, $E$2:$E$747, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -7147,12 +7134,12 @@
       </c>
       <c r="J128" s="36"/>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B128, $C$2:$C$747, C128, $D$2:$D$747, D128, $E$2:$E$747, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="25"/>
     </row>
-    <row r="129" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3">
         <v>46262.375</v>
       </c>
@@ -7194,12 +7181,12 @@
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B129, $C$2:$C$747, C129, $D$2:$D$747, D129, $E$2:$E$747, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P129" s="10"/>
     </row>
-    <row r="130" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -7241,14 +7228,14 @@
         <v>500</v>
       </c>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B130, $C$2:$C$747, C130, $D$2:$D$747, D130, $E$2:$E$747, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="7">IF(COUNTIFS( $B$2:$B$747, B130, $C$2:$C$747, C130, $D$2:$D$747, D130, $E$2:$E$747, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="42" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="8" t="s">
         <v>62</v>
       </c>
@@ -7278,11 +7265,11 @@
       </c>
       <c r="J131" s="36"/>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B131, $C$2:$C$747, C131, $D$2:$D$747, D131, $E$2:$E$747, E131) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -7320,15 +7307,15 @@
         <v>9470</v>
       </c>
       <c r="M132" s="18">
-        <f>ABS((D132*E132)-L132)</f>
+        <f t="shared" ref="M132:M142" si="8">ABS((D132*E132)-L132)</f>
         <v>300</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B132, $C$2:$C$747, C132, $D$2:$D$747, D132, $E$2:$E$747, E132) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="32">
         <v>46267.425694444442</v>
       </c>
@@ -7366,11 +7353,11 @@
         <v>4120</v>
       </c>
       <c r="M133" s="29">
-        <f>ABS((D133*E133)-L133)</f>
+        <f t="shared" si="8"/>
         <v>270</v>
       </c>
       <c r="N133" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B133, $C$2:$C$747, C133, $D$2:$D$747, D133, $E$2:$E$747, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="30" t="s">
@@ -7378,7 +7365,7 @@
       </c>
       <c r="P133" s="31"/>
     </row>
-    <row r="134" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="32">
         <v>46280.593055555553</v>
       </c>
@@ -7416,18 +7403,18 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M134" s="29">
-        <f>ABS((D134*E134)-L134)</f>
+        <f t="shared" si="8"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N134" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B134, $C$2:$C$747, C134, $D$2:$D$747, D134, $E$2:$E$747, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="30" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -7465,15 +7452,15 @@
         <v>10249</v>
       </c>
       <c r="M135" s="18">
-        <f>ABS((D135*E135)-L135)</f>
+        <f t="shared" si="8"/>
         <v>4451</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B135, $C$2:$C$747, C135, $D$2:$D$747, D135, $E$2:$E$747, E135) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3">
         <v>46266.642361111109</v>
       </c>
@@ -7487,7 +7474,7 @@
         <v>100</v>
       </c>
       <c r="E136" s="4">
-        <v>344.3</v>
+        <v>344.5</v>
       </c>
       <c r="F136" s="4">
         <v>8.9556962030000005</v>
@@ -7511,15 +7498,15 @@
         <v>33950</v>
       </c>
       <c r="M136" s="18">
-        <f>ABS((D136*E136)-L136)</f>
-        <v>480</v>
+        <f t="shared" si="8"/>
+        <v>500</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B136, $C$2:$C$747, C136, $D$2:$D$747, D136, $E$2:$E$747, E136) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -7557,18 +7544,18 @@
         <v>18140</v>
       </c>
       <c r="M137" s="27">
-        <f>ABS((D137*E137)-L137)</f>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N137" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B137, $C$2:$C$747, C137, $D$2:$D$747, D137, $E$2:$E$747, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3">
         <v>46280.575694444444</v>
       </c>
@@ -7606,15 +7593,15 @@
         <v>23450</v>
       </c>
       <c r="M138" s="18">
-        <f>ABS((D138*E138)-L138)</f>
+        <f t="shared" si="8"/>
         <v>1500</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B138, $C$2:$C$747, C138, $D$2:$D$747, D138, $E$2:$E$747, E138) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3">
         <v>46281.402777777781</v>
       </c>
@@ -7652,15 +7639,15 @@
         <v>4410</v>
       </c>
       <c r="M139" s="18">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" si="8"/>
         <v>580</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B139, $C$2:$C$747, C139, $D$2:$D$747, D139, $E$2:$E$747, E139) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -7698,18 +7685,18 @@
         <v>73800</v>
       </c>
       <c r="M140" s="18">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="8"/>
         <v>48320</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B140, $C$2:$C$747, C140, $D$2:$D$747, D140, $E$2:$E$747, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3">
         <v>46261.375</v>
       </c>
@@ -7747,15 +7734,15 @@
         <v>10510</v>
       </c>
       <c r="M141" s="18">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B141, $C$2:$C$747, C141, $D$2:$D$747, D141, $E$2:$E$747, E141) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46335.442361111112</v>
       </c>
@@ -7793,15 +7780,15 @@
         <v>14100</v>
       </c>
       <c r="M142" s="18">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B142, $C$2:$C$747, C142, $D$2:$D$747, D142, $E$2:$E$747, E142) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="46" t="s">
         <v>62</v>
       </c>
@@ -7836,7 +7823,7 @@
       <c r="L143" s="47"/>
       <c r="M143" s="47"/>
       <c r="N143" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B143, $C$2:$C$747, C143, $D$2:$D$747, D143, $E$2:$E$747, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="25"/>
@@ -7844,7 +7831,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="32">
         <v>46335.62777777778</v>
       </c>
@@ -7882,17 +7869,17 @@
         <v>5370</v>
       </c>
       <c r="M144" s="29">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" ref="M144:M154" si="9">ABS((D144*E144)-L144)</f>
         <v>320</v>
       </c>
       <c r="N144" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B144, $C$2:$C$747, C144, $D$2:$D$747, D144, $E$2:$E$747, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="31"/>
       <c r="P144" s="31"/>
     </row>
-    <row r="145" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="32">
         <v>46280.375694444447</v>
       </c>
@@ -7930,15 +7917,15 @@
         <v>2610</v>
       </c>
       <c r="M145" s="29">
-        <f>ABS((D145*E145)-L145)</f>
+        <f t="shared" si="9"/>
         <v>235</v>
       </c>
       <c r="N145" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B145, $C$2:$C$747, C145, $D$2:$D$747, D145, $E$2:$E$747, E145) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="32">
         <v>46272.451388888891</v>
       </c>
@@ -7976,17 +7963,17 @@
         <v>8820</v>
       </c>
       <c r="M146" s="29">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" si="9"/>
         <v>650</v>
       </c>
       <c r="N146" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B146, $C$2:$C$747, C146, $D$2:$D$747, D146, $E$2:$E$747, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="31"/>
       <c r="P146" s="31"/>
     </row>
-    <row r="147" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="32">
         <v>46272.390972222223</v>
       </c>
@@ -8024,15 +8011,15 @@
         <v>36946</v>
       </c>
       <c r="M147" s="29">
-        <f>ABS((D147*E147)-L147)</f>
+        <f t="shared" si="9"/>
         <v>934</v>
       </c>
       <c r="N147" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B147, $C$2:$C$747, C147, $D$2:$D$747, D147, $E$2:$E$747, E147) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -8070,17 +8057,17 @@
         <v>7578</v>
       </c>
       <c r="M148" s="29">
-        <f>ABS((D148*E148)-L148)</f>
+        <f t="shared" si="9"/>
         <v>294</v>
       </c>
       <c r="N148" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B148, $C$2:$C$747, C148, $D$2:$D$747, D148, $E$2:$E$747, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O148" s="10"/>
       <c r="P148" s="10"/>
     </row>
-    <row r="149" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="32">
         <v>46266.375694444447</v>
       </c>
@@ -8118,17 +8105,17 @@
         <v>7578</v>
       </c>
       <c r="M149" s="29">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" si="9"/>
         <v>294</v>
       </c>
       <c r="N149" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B149, $C$2:$C$747, C149, $D$2:$D$747, D149, $E$2:$E$747, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O149" s="10"/>
       <c r="P149" s="10"/>
     </row>
-    <row r="150" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="32">
         <v>46267.424305555556</v>
       </c>
@@ -8166,17 +8153,17 @@
         <v>4968</v>
       </c>
       <c r="M150" s="29">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="9"/>
         <v>280</v>
       </c>
       <c r="N150" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B150, $C$2:$C$747, C150, $D$2:$D$747, D150, $E$2:$E$747, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="31"/>
       <c r="P150" s="31"/>
     </row>
-    <row r="151" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -8214,15 +8201,15 @@
         <v>3810</v>
       </c>
       <c r="M151" s="18">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N151" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B151, $C$2:$C$747, C151, $D$2:$D$747, D151, $E$2:$E$747, E151) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3">
         <v>46261.375</v>
       </c>
@@ -8260,16 +8247,16 @@
         <v>34100</v>
       </c>
       <c r="M152" s="18">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" si="9"/>
         <v>700</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B152, $C$2:$C$747, C152, $D$2:$D$747, D152, $E$2:$E$747, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="31"/>
     </row>
-    <row r="153" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="11">
         <v>46243.375</v>
       </c>
@@ -8307,11 +8294,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M153" s="29">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="9"/>
         <v>710.99999999999636</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B153, $C$2:$C$747, C153, $D$2:$D$747, D153, $E$2:$E$747, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="41" t="s">
@@ -8319,7 +8306,7 @@
       </c>
       <c r="P153"/>
     </row>
-    <row r="154" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46276.4</v>
       </c>
@@ -8357,15 +8344,15 @@
         <v>14200</v>
       </c>
       <c r="M154" s="18">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="9"/>
         <v>500</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B154, $C$2:$C$747, C154, $D$2:$D$747, D154, $E$2:$E$747, E154) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="8" t="s">
         <v>62</v>
       </c>
@@ -8395,11 +8382,11 @@
       </c>
       <c r="J155" s="36"/>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B155, $C$2:$C$747, C155, $D$2:$D$747, D155, $E$2:$E$747, E155) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -8441,11 +8428,11 @@
         <v>250</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B156, $C$2:$C$747, C156, $D$2:$D$747, D156, $E$2:$E$747, E156) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -8487,11 +8474,11 @@
         <v>300</v>
       </c>
       <c r="N157" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B157, $C$2:$C$747, C157, $D$2:$D$747, D157, $E$2:$E$747, E157) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="3">
         <v>46261.375</v>
       </c>
@@ -8533,11 +8520,11 @@
         <v>300</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B158, $C$2:$C$747, C158, $D$2:$D$747, D158, $E$2:$E$747, E158) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -8579,11 +8566,11 @@
         <v>275</v>
       </c>
       <c r="N159" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B159, $C$2:$C$747, C159, $D$2:$D$747, D159, $E$2:$E$747, E159) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="11">
         <v>46252.6875</v>
       </c>
@@ -8618,13 +8605,13 @@
       <c r="L160" s="18"/>
       <c r="M160" s="18"/>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B160, $C$2:$C$747, C160, $D$2:$D$747, D160, $E$2:$E$747, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="10"/>
       <c r="P160" s="10"/>
     </row>
-    <row r="161" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="8" t="s">
         <v>62</v>
       </c>
@@ -8659,13 +8646,13 @@
       <c r="L161" s="18"/>
       <c r="M161" s="18"/>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B161, $C$2:$C$747, C161, $D$2:$D$747, D161, $E$2:$E$747, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="10"/>
       <c r="P161" s="10"/>
     </row>
-    <row r="162" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8693,13 +8680,13 @@
       <c r="I162" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J162" s="55"/>
+      <c r="J162" s="36"/>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B162, $C$2:$C$747, C162, $D$2:$D$747, D162, $E$2:$E$747, E162) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -8741,14 +8728,14 @@
         <v>47900</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B163, $C$2:$C$747, C163, $D$2:$D$747, D163, $E$2:$E$747, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O163" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="164" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8780,11 +8767,11 @@
         <v>117</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B164, $C$2:$C$747, C164, $D$2:$D$747, D164, $E$2:$E$747, E164) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3">
         <v>46266.375</v>
       </c>
@@ -8822,18 +8809,18 @@
         <v>25300</v>
       </c>
       <c r="M165" s="18">
-        <f>ABS((D165*E165)-L165)</f>
+        <f t="shared" ref="M165:M170" si="10">ABS((D165*E165)-L165)</f>
         <v>650</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B165, $C$2:$C$747, C165, $D$2:$D$747, D165, $E$2:$E$747, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O165" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="166" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -8871,11 +8858,11 @@
         <v>12480</v>
       </c>
       <c r="M166" s="18">
-        <f>ABS((D166*E166)-L166)</f>
+        <f t="shared" si="10"/>
         <v>495</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B166, $C$2:$C$747, C166, $D$2:$D$747, D166, $E$2:$E$747, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O166" s="41" t="s">
@@ -8883,7 +8870,7 @@
       </c>
       <c r="P166" s="10"/>
     </row>
-    <row r="167" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="35">
         <v>46255</v>
       </c>
@@ -8921,16 +8908,16 @@
         <v>4680</v>
       </c>
       <c r="M167" s="29">
-        <f>ABS((D167*E167)-L167)</f>
+        <f t="shared" si="10"/>
         <v>140</v>
       </c>
       <c r="N167" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B167, $C$2:$C$747, C167, $D$2:$D$747, D167, $E$2:$E$747, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="P167" s="31"/>
     </row>
-    <row r="168" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="32">
         <v>46261.385416666664</v>
       </c>
@@ -8968,11 +8955,11 @@
         <v>4520</v>
       </c>
       <c r="M168" s="29">
-        <f>ABS((D168*E168)-L168)</f>
+        <f t="shared" si="10"/>
         <v>300</v>
       </c>
       <c r="N168" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B168, $C$2:$C$747, C168, $D$2:$D$747, D168, $E$2:$E$747, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -9014,15 +9001,18 @@
         <v>8049</v>
       </c>
       <c r="M169" s="18">
-        <f>ABS((D169*E169)-L169)</f>
+        <f t="shared" si="10"/>
         <v>800</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B169, $C$2:$C$747, C169, $D$2:$D$747, D169, $E$2:$E$747, E169) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+      <c r="O169" s="41" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -9060,15 +9050,15 @@
         <v>12510</v>
       </c>
       <c r="M170" s="18">
-        <f>ABS((D170*E170)-L170)</f>
+        <f t="shared" si="10"/>
         <v>290</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B170, $C$2:$C$747, C170, $D$2:$D$747, D170, $E$2:$E$747, E170) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9098,11 +9088,11 @@
       </c>
       <c r="J171" s="36"/>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B171, $C$2:$C$747, C171, $D$2:$D$747, D171, $E$2:$E$747, E171) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -9144,12 +9134,12 @@
         <v>1000</v>
       </c>
       <c r="N172" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B172, $C$2:$C$747, C172, $D$2:$D$747, D172, $E$2:$E$747, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P172" s="31"/>
     </row>
-    <row r="173" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="11">
         <v>46253.375</v>
       </c>
@@ -9184,11 +9174,11 @@
         <v>145</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B173, $C$2:$C$747, C173, $D$2:$D$747, D173, $E$2:$E$747, E173) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -9230,7 +9220,7 @@
         <v>300</v>
       </c>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B174, $C$2:$C$747, C174, $D$2:$D$747, D174, $E$2:$E$747, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O174" s="41" t="s">
@@ -9238,7 +9228,7 @@
       </c>
       <c r="P174"/>
     </row>
-    <row r="175" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="8" t="s">
         <v>62</v>
       </c>
@@ -9268,11 +9258,11 @@
       </c>
       <c r="J175" s="36"/>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B175, $C$2:$C$747, C175, $D$2:$D$747, D175, $E$2:$E$747, E175) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3">
         <v>46276.390277777777</v>
       </c>
@@ -9310,15 +9300,15 @@
         <v>14400</v>
       </c>
       <c r="M176" s="18">
-        <f>ABS((D176*E176)-L176)</f>
+        <f t="shared" ref="M176:M182" si="11">ABS((D176*E176)-L176)</f>
         <v>500</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B176, $C$2:$C$747, C176, $D$2:$D$747, D176, $E$2:$E$747, E176) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3">
         <v>46266.375</v>
       </c>
@@ -9356,11 +9346,11 @@
         <v>14552</v>
       </c>
       <c r="M177" s="18">
-        <f>ABS((D177*E177)-L177)</f>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B177, $C$2:$C$747, C177, $D$2:$D$747, D177, $E$2:$E$747, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="41" t="s">
@@ -9368,7 +9358,7 @@
       </c>
       <c r="P177" s="31"/>
     </row>
-    <row r="178" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="32">
         <v>46260.556944444441</v>
       </c>
@@ -9406,15 +9396,15 @@
         <v>6105</v>
       </c>
       <c r="M178" s="29">
-        <f>ABS((D178*E178)-L178)</f>
+        <f t="shared" si="11"/>
         <v>150</v>
       </c>
       <c r="N178" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B178, $C$2:$C$747, C178, $D$2:$D$747, D178, $E$2:$E$747, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="179" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="32">
         <v>46261.375</v>
       </c>
@@ -9452,17 +9442,17 @@
         <v>6005</v>
       </c>
       <c r="M179" s="29">
-        <f>ABS((D179*E179)-L179)</f>
+        <f t="shared" si="11"/>
         <v>250</v>
       </c>
       <c r="N179" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B179, $C$2:$C$747, C179, $D$2:$D$747, D179, $E$2:$E$747, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O179" s="10"/>
       <c r="P179" s="10"/>
     </row>
-    <row r="180" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -9500,16 +9490,16 @@
         <v>5520</v>
       </c>
       <c r="M180" s="29">
-        <f>ABS((D180*E180)-L180)</f>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="N180" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B180, $C$2:$C$747, C180, $D$2:$D$747, D180, $E$2:$E$747, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P180" s="10"/>
     </row>
-    <row r="181" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="43">
         <v>46243.505555555559</v>
       </c>
@@ -9547,16 +9537,16 @@
         <v>2657</v>
       </c>
       <c r="M181" s="29">
-        <f>ABS((D181*E181)-L181)</f>
+        <f t="shared" si="11"/>
         <v>253</v>
       </c>
       <c r="N181" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B181, $C$2:$C$747, C181, $D$2:$D$747, D181, $E$2:$E$747, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O181" s="31"/>
     </row>
-    <row r="182" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="32">
         <v>46280.588194444441</v>
       </c>
@@ -9594,17 +9584,17 @@
         <v>2554.5</v>
       </c>
       <c r="M182" s="29">
-        <f>ABS((D182*E182)-L182)</f>
+        <f t="shared" si="11"/>
         <v>355.5</v>
       </c>
       <c r="N182" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B182, $C$2:$C$747, C182, $D$2:$D$747, D182, $E$2:$E$747, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O182" s="31"/>
       <c r="P182" s="31"/>
     </row>
-    <row r="183" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="8" t="s">
         <v>62</v>
       </c>
@@ -9636,11 +9626,11 @@
         <v>117</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B183, $C$2:$C$747, C183, $D$2:$D$747, D183, $E$2:$E$747, E183) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3">
         <v>46276.375</v>
       </c>
@@ -9682,11 +9672,11 @@
         <v>816</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B184, $C$2:$C$747, C184, $D$2:$D$747, D184, $E$2:$E$747, E184) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -9728,13 +9718,13 @@
         <v>650</v>
       </c>
       <c r="N185" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B185, $C$2:$C$747, C185, $D$2:$D$747, D185, $E$2:$E$747, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O185"/>
       <c r="P185"/>
     </row>
-    <row r="186" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -9776,14 +9766,14 @@
         <v>501</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B186, $C$2:$C$747, C186, $D$2:$D$747, D186, $E$2:$E$747, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O186" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="187" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="8" t="s">
         <v>62</v>
       </c>
@@ -9815,12 +9805,12 @@
         <v>118</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B187, $C$2:$C$747, C187, $D$2:$D$747, D187, $E$2:$E$747, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O187" s="31"/>
     </row>
-    <row r="188" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -9862,7 +9852,7 @@
         <v>650</v>
       </c>
       <c r="N188" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B188, $C$2:$C$747, C188, $D$2:$D$747, D188, $E$2:$E$747, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O188" s="41" t="s">
@@ -9870,7 +9860,7 @@
       </c>
       <c r="P188" s="31"/>
     </row>
-    <row r="189" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3">
         <v>46269.375</v>
       </c>
@@ -9912,11 +9902,11 @@
         <v>250</v>
       </c>
       <c r="N189" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B189, $C$2:$C$747, C189, $D$2:$D$747, D189, $E$2:$E$747, E189) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="11">
         <v>46253.375</v>
       </c>
@@ -9953,13 +9943,13 @@
       <c r="L190" s="18"/>
       <c r="M190" s="18"/>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B190, $C$2:$C$747, C190, $D$2:$D$747, D190, $E$2:$E$747, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="10"/>
       <c r="P190" s="10"/>
     </row>
-    <row r="191" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9992,12 +9982,12 @@
       <c r="L191" s="18"/>
       <c r="M191" s="18"/>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B191, $C$2:$C$747, C191, $D$2:$D$747, D191, $E$2:$E$747, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P191" s="10"/>
     </row>
-    <row r="192" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10029,14 +10019,14 @@
         <v>118</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B192, $C$2:$C$747, C192, $D$2:$D$747, D192, $E$2:$E$747, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -10078,11 +10068,11 @@
         <v>47480</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B193, $C$2:$C$747, C193, $D$2:$D$747, D193, $E$2:$E$747, E193) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10124,11 +10114,11 @@
         <v>260</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B194, $C$2:$C$747, C194, $D$2:$D$747, D194, $E$2:$E$747, E194) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N194:N257" si="12">IF(COUNTIFS( $B$2:$B$747, B194, $C$2:$C$747, C194, $D$2:$D$747, D194, $E$2:$E$747, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3">
         <v>46262.375</v>
       </c>
@@ -10170,11 +10160,11 @@
         <v>320</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B195, $C$2:$C$747, C195, $D$2:$D$747, D195, $E$2:$E$747, E195) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3">
         <v>46265.486111111109</v>
       </c>
@@ -10216,11 +10206,11 @@
         <v>448</v>
       </c>
       <c r="N196" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B196, $C$2:$C$747, C196, $D$2:$D$747, D196, $E$2:$E$747, E196) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3">
         <v>46266.375</v>
       </c>
@@ -10262,11 +10252,11 @@
         <v>360</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B197, $C$2:$C$747, C197, $D$2:$D$747, D197, $E$2:$E$747, E197) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="9" t="s">
         <v>62</v>
       </c>
@@ -10296,11 +10286,11 @@
       </c>
       <c r="J198" s="36"/>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B198, $C$2:$C$747, C198, $D$2:$D$747, D198, $E$2:$E$747, E198) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10342,11 +10332,11 @@
         <v>340</v>
       </c>
       <c r="N199" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B199, $C$2:$C$747, C199, $D$2:$D$747, D199, $E$2:$E$747, E199) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="11">
         <v>46252.6875</v>
       </c>
@@ -10378,11 +10368,11 @@
         <v>118</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B200, $C$2:$C$747, C200, $D$2:$D$747, D200, $E$2:$E$747, E200) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="201" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -10412,12 +10402,12 @@
       </c>
       <c r="J201" s="36"/>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B201, $C$2:$C$747, C201, $D$2:$D$747, D201, $E$2:$E$747, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O201" s="31"/>
     </row>
-    <row r="202" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -10459,13 +10449,13 @@
         <v>300</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B202, $C$2:$C$747, C202, $D$2:$D$747, D202, $E$2:$E$747, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="10"/>
       <c r="P202" s="10"/>
     </row>
-    <row r="203" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -10507,11 +10497,11 @@
         <v>940</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B203, $C$2:$C$747, C203, $D$2:$D$747, D203, $E$2:$E$747, E203) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46274.375</v>
       </c>
@@ -10553,11 +10543,11 @@
         <v>651</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B204, $C$2:$C$747, C204, $D$2:$D$747, D204, $E$2:$E$747, E204) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="8" t="s">
         <v>62</v>
       </c>
@@ -10589,11 +10579,11 @@
         <v>118</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B205, $C$2:$C$747, C205, $D$2:$D$747, D205, $E$2:$E$747, E205) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="3">
         <v>46260.375</v>
       </c>
@@ -10635,11 +10625,11 @@
         <v>800</v>
       </c>
       <c r="N206" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B206, $C$2:$C$747, C206, $D$2:$D$747, D206, $E$2:$E$747, E206) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="207" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="32">
         <v>46258.443749999999</v>
       </c>
@@ -10681,11 +10671,11 @@
         <v>527.5</v>
       </c>
       <c r="N207" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B207, $C$2:$C$747, C207, $D$2:$D$747, D207, $E$2:$E$747, E207) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="43">
         <v>46253.4</v>
       </c>
@@ -10722,13 +10712,13 @@
       <c r="L208" s="29"/>
       <c r="M208" s="29"/>
       <c r="N208" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B208, $C$2:$C$747, C208, $D$2:$D$747, D208, $E$2:$E$747, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="31"/>
       <c r="P208" s="31"/>
     </row>
-    <row r="209" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="8" t="s">
         <v>62</v>
       </c>
@@ -10760,11 +10750,11 @@
         <v>117</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B209, $C$2:$C$747, C209, $D$2:$D$747, D209, $E$2:$E$747, E209) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3">
         <v>46276.388194444444</v>
       </c>
@@ -10806,11 +10796,11 @@
         <v>450</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B210, $C$2:$C$747, C210, $D$2:$D$747, D210, $E$2:$E$747, E210) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -10852,7 +10842,7 @@
         <v>300</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B211, $C$2:$C$747, C211, $D$2:$D$747, D211, $E$2:$E$747, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10898,12 +10888,12 @@
         <v>250</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B212, $C$2:$C$747, C212, $D$2:$D$747, D212, $E$2:$E$747, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="P212" s="31"/>
     </row>
-    <row r="213" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="8" t="s">
         <v>62</v>
       </c>
@@ -10935,11 +10925,11 @@
         <v>118</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B213, $C$2:$C$747, C213, $D$2:$D$747, D213, $E$2:$E$747, E213) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="32">
         <v>46258.443055555559</v>
       </c>
@@ -10981,13 +10971,13 @@
         <v>300</v>
       </c>
       <c r="N214" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B214, $C$2:$C$747, C214, $D$2:$D$747, D214, $E$2:$E$747, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="31"/>
       <c r="P214" s="31"/>
     </row>
-    <row r="215" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="32">
         <v>46259.375</v>
       </c>
@@ -11029,13 +11019,13 @@
         <v>188</v>
       </c>
       <c r="N215" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B215, $C$2:$C$747, C215, $D$2:$D$747, D215, $E$2:$E$747, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="31"/>
       <c r="P215" s="31"/>
     </row>
-    <row r="216" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3">
         <v>46262.375</v>
       </c>
@@ -11077,11 +11067,11 @@
         <v>300</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B216, $C$2:$C$747, C216, $D$2:$D$747, D216, $E$2:$E$747, E216) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="8" t="s">
         <v>62</v>
       </c>
@@ -11113,11 +11103,11 @@
         <v>118</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B217, $C$2:$C$747, C217, $D$2:$D$747, D217, $E$2:$E$747, E217) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="8" t="s">
         <v>62</v>
       </c>
@@ -11149,11 +11139,11 @@
         <v>118</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B218, $C$2:$C$747, C218, $D$2:$D$747, D218, $E$2:$E$747, E218) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="219" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="3">
         <v>46259.375</v>
       </c>
@@ -11195,12 +11185,12 @@
         <v>650</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B219, $C$2:$C$747, C219, $D$2:$D$747, D219, $E$2:$E$747, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O219" s="31"/>
     </row>
-    <row r="220" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11230,11 +11220,11 @@
       </c>
       <c r="J220" s="36"/>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B220, $C$2:$C$747, C220, $D$2:$D$747, D220, $E$2:$E$747, E220) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="221" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -11276,14 +11266,14 @@
         <v>500</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B221, $C$2:$C$747, C221, $D$2:$D$747, D221, $E$2:$E$747, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="222" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="11">
         <v>46243.375</v>
       </c>
@@ -11325,12 +11315,12 @@
         <v>300</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B222, $C$2:$C$747, C222, $D$2:$D$747, D222, $E$2:$E$747, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="P222" s="26"/>
     </row>
-    <row r="223" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="8" t="s">
         <v>62</v>
       </c>
@@ -11362,11 +11352,11 @@
         <v>55</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B223, $C$2:$C$747, C223, $D$2:$D$747, D223, $E$2:$E$747, E223) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -11403,11 +11393,11 @@
       <c r="L224" s="17"/>
       <c r="M224" s="17"/>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B224, $C$2:$C$747, C224, $D$2:$D$747, D224, $E$2:$E$747, E224) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="225" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11437,12 +11427,12 @@
       </c>
       <c r="J225" s="36"/>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B225, $C$2:$C$747, C225, $D$2:$D$747, D225, $E$2:$E$747, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="P225" s="31"/>
     </row>
-    <row r="226" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="8" t="s">
         <v>62</v>
       </c>
@@ -11477,12 +11467,12 @@
       <c r="L226" s="18"/>
       <c r="M226" s="18"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B226, $C$2:$C$747, C226, $D$2:$D$747, D226, $E$2:$E$747, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O226" s="10"/>
     </row>
-    <row r="227" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -11524,11 +11514,11 @@
         <v>400</v>
       </c>
       <c r="N227" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B227, $C$2:$C$747, C227, $D$2:$D$747, D227, $E$2:$E$747, E227) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="228" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -11560,11 +11550,11 @@
         <v>117</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B228, $C$2:$C$747, C228, $D$2:$D$747, D228, $E$2:$E$747, E228) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="11">
         <v>46252.6875</v>
       </c>
@@ -11596,11 +11586,11 @@
         <v>117</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B229, $C$2:$C$747, C229, $D$2:$D$747, D229, $E$2:$E$747, E229) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="8" t="s">
         <v>62</v>
       </c>
@@ -11630,11 +11620,11 @@
       </c>
       <c r="J230" s="36"/>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B230, $C$2:$C$747, C230, $D$2:$D$747, D230, $E$2:$E$747, E230) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -11676,14 +11666,14 @@
         <v>646</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B231, $C$2:$C$747, C231, $D$2:$D$747, D231, $E$2:$E$747, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O231" s="41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="232" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="11">
         <v>46252.6875</v>
       </c>
@@ -11715,11 +11705,11 @@
         <v>154</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B232, $C$2:$C$747, C232, $D$2:$D$747, D232, $E$2:$E$747, E232) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11751,11 +11741,11 @@
         <v>118</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B233, $C$2:$C$747, C233, $D$2:$D$747, D233, $E$2:$E$747, E233) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="8" t="s">
         <v>62</v>
       </c>
@@ -11785,11 +11775,11 @@
       </c>
       <c r="J234" s="36"/>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B234, $C$2:$C$747, C234, $D$2:$D$747, D234, $E$2:$E$747, E234) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="8" t="s">
         <v>62</v>
       </c>
@@ -11824,7 +11814,7 @@
       <c r="L235" s="18"/>
       <c r="M235" s="18"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B235, $C$2:$C$747, C235, $D$2:$D$747, D235, $E$2:$E$747, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="10"/>
@@ -11872,11 +11862,11 @@
         <v>1800</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B236, $C$2:$C$747, C236, $D$2:$D$747, D236, $E$2:$E$747, E236) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="3">
         <v>46260.375</v>
       </c>
@@ -11918,12 +11908,12 @@
         <v>650</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B237, $C$2:$C$747, C237, $D$2:$D$747, D237, $E$2:$E$747, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="P237" s="31"/>
     </row>
-    <row r="238" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="3">
         <v>46276.375</v>
       </c>
@@ -11965,11 +11955,11 @@
         <v>450</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B238, $C$2:$C$747, C238, $D$2:$D$747, D238, $E$2:$E$747, E238) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12001,11 +11991,11 @@
         <v>55</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B239, $C$2:$C$747, C239, $D$2:$D$747, D239, $E$2:$E$747, E239) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="11">
         <v>46252.6875</v>
       </c>
@@ -12037,11 +12027,11 @@
         <v>117</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B240, $C$2:$C$747, C240, $D$2:$D$747, D240, $E$2:$E$747, E240) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="3">
         <v>46262.375</v>
       </c>
@@ -12083,12 +12073,12 @@
         <v>370</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B241, $C$2:$C$747, C241, $D$2:$D$747, D241, $E$2:$E$747, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="P241" s="31"/>
     </row>
-    <row r="242" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="11">
         <v>46252.6875</v>
       </c>
@@ -12120,12 +12110,12 @@
         <v>118</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B242, $C$2:$C$747, C242, $D$2:$D$747, D242, $E$2:$E$747, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O242" s="31"/>
     </row>
-    <row r="243" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3">
         <v>46261.375</v>
       </c>
@@ -12167,11 +12157,11 @@
         <v>260</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B243, $C$2:$C$747, C243, $D$2:$D$747, D243, $E$2:$E$747, E243) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="8" t="s">
         <v>62</v>
       </c>
@@ -12203,11 +12193,11 @@
         <v>118</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B244, $C$2:$C$747, C244, $D$2:$D$747, D244, $E$2:$E$747, E244) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="8" t="s">
         <v>62</v>
       </c>
@@ -12237,11 +12227,11 @@
       </c>
       <c r="J245" s="36"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B245, $C$2:$C$747, C245, $D$2:$D$747, D245, $E$2:$E$747, E245) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="8" t="s">
         <v>62</v>
       </c>
@@ -12273,11 +12263,11 @@
         <v>117</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B246, $C$2:$C$747, C246, $D$2:$D$747, D246, $E$2:$E$747, E246) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -12319,11 +12309,11 @@
         <v>480</v>
       </c>
       <c r="N247" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B247, $C$2:$C$747, C247, $D$2:$D$747, D247, $E$2:$E$747, E247) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="8" t="s">
         <v>62</v>
       </c>
@@ -12353,11 +12343,11 @@
       </c>
       <c r="J248" s="36"/>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B248, $C$2:$C$747, C248, $D$2:$D$747, D248, $E$2:$E$747, E248) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="8" t="s">
         <v>62</v>
       </c>
@@ -12389,12 +12379,12 @@
         <v>118</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B249, $C$2:$C$747, C249, $D$2:$D$747, D249, $E$2:$E$747, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="12"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="31"/>
     </row>
-    <row r="250" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12429,11 +12419,11 @@
         <v>146</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B250, $C$2:$C$747, C250, $D$2:$D$747, D250, $E$2:$E$747, E250) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -12475,11 +12465,11 @@
         <v>300</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B251, $C$2:$C$747, C251, $D$2:$D$747, D251, $E$2:$E$747, E251) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="20">
         <v>46255</v>
       </c>
@@ -12521,11 +12511,11 @@
         <v>300</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B252, $C$2:$C$747, C252, $D$2:$D$747, D252, $E$2:$E$747, E252) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="253" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="3">
         <v>46262.375</v>
       </c>
@@ -12567,11 +12557,11 @@
         <v>300</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B253, $C$2:$C$747, C253, $D$2:$D$747, D253, $E$2:$E$747, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="8" t="s">
         <v>62</v>
       </c>
@@ -12601,11 +12591,11 @@
       </c>
       <c r="J254" s="36"/>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B254, $C$2:$C$747, C254, $D$2:$D$747, D254, $E$2:$E$747, E254) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="255" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="8" t="s">
         <v>62</v>
       </c>
@@ -12637,11 +12627,11 @@
         <v>117</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B255, $C$2:$C$747, C255, $D$2:$D$747, D255, $E$2:$E$747, E255) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="8" t="s">
         <v>62</v>
       </c>
@@ -12671,11 +12661,11 @@
       </c>
       <c r="J256" s="36"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B256, $C$2:$C$747, C256, $D$2:$D$747, D256, $E$2:$E$747, E256) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="8" t="s">
         <v>62</v>
       </c>
@@ -12705,11 +12695,11 @@
       </c>
       <c r="J257" s="36"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B257, $C$2:$C$747, C257, $D$2:$D$747, D257, $E$2:$E$747, E257) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="258" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="12"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="3">
         <v>46269.643055555556</v>
       </c>
@@ -12751,11 +12741,11 @@
         <v>268</v>
       </c>
       <c r="N258" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B258, $C$2:$C$747, C258, $D$2:$D$747, D258, $E$2:$E$747, E258) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N258:N297" si="13">IF(COUNTIFS( $B$2:$B$747, B258, $C$2:$C$747, C258, $D$2:$D$747, D258, $E$2:$E$747, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
         <v>62</v>
       </c>
@@ -12785,7 +12775,7 @@
       </c>
       <c r="J259" s="36"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B259, $C$2:$C$747, C259, $D$2:$D$747, D259, $E$2:$E$747, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12831,7 +12821,7 @@
         <v>285</v>
       </c>
       <c r="N260" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B260, $C$2:$C$747, C260, $D$2:$D$747, D260, $E$2:$E$747, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12877,11 +12867,11 @@
         <v>726</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B261, $C$2:$C$747, C261, $D$2:$D$747, D261, $E$2:$E$747, E261) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="8" t="s">
         <v>62</v>
       </c>
@@ -12911,11 +12901,11 @@
       </c>
       <c r="J262" s="36"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B262, $C$2:$C$747, C262, $D$2:$D$747, D262, $E$2:$E$747, E262) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="8" t="s">
         <v>62</v>
       </c>
@@ -12947,11 +12937,11 @@
         <v>118</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B263, $C$2:$C$747, C263, $D$2:$D$747, D263, $E$2:$E$747, E263) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="264" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="8" t="s">
         <v>62</v>
       </c>
@@ -12981,12 +12971,12 @@
       </c>
       <c r="J264" s="36"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B264, $C$2:$C$747, C264, $D$2:$D$747, D264, $E$2:$E$747, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P264" s="31"/>
     </row>
-    <row r="265" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -13028,11 +13018,11 @@
         <v>250</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B265, $C$2:$C$747, C265, $D$2:$D$747, D265, $E$2:$E$747, E265) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="8" t="s">
         <v>62</v>
       </c>
@@ -13062,7 +13052,7 @@
       </c>
       <c r="J266" s="36"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B266, $C$2:$C$747, C266, $D$2:$D$747, D266, $E$2:$E$747, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13108,11 +13098,11 @@
         <v>275</v>
       </c>
       <c r="N267" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B267, $C$2:$C$747, C267, $D$2:$D$747, D267, $E$2:$E$747, E267) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="8" t="s">
         <v>62</v>
       </c>
@@ -13142,11 +13132,11 @@
       </c>
       <c r="J268" s="36"/>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B268, $C$2:$C$747, C268, $D$2:$D$747, D268, $E$2:$E$747, E268) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="8" t="s">
         <v>62</v>
       </c>
@@ -13178,11 +13168,11 @@
         <v>117</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B269, $C$2:$C$747, C269, $D$2:$D$747, D269, $E$2:$E$747, E269) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="3">
         <v>46260.375</v>
       </c>
@@ -13224,11 +13214,11 @@
         <v>300</v>
       </c>
       <c r="N270" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B270, $C$2:$C$747, C270, $D$2:$D$747, D270, $E$2:$E$747, E270) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="8" t="s">
         <v>62</v>
       </c>
@@ -13258,11 +13248,11 @@
       </c>
       <c r="J271" s="36"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B271, $C$2:$C$747, C271, $D$2:$D$747, D271, $E$2:$E$747, E271) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -13304,11 +13294,11 @@
         <v>250</v>
       </c>
       <c r="N272" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B272, $C$2:$C$747, C272, $D$2:$D$747, D272, $E$2:$E$747, E272) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="8" t="s">
         <v>62</v>
       </c>
@@ -13341,13 +13331,13 @@
       <c r="L273" s="18"/>
       <c r="M273" s="18"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B273, $C$2:$C$747, C273, $D$2:$D$747, D273, $E$2:$E$747, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O273" s="10"/>
       <c r="P273" s="10"/>
     </row>
-    <row r="274" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="8" t="s">
         <v>62</v>
       </c>
@@ -13380,13 +13370,13 @@
       <c r="L274" s="18"/>
       <c r="M274" s="18"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B274, $C$2:$C$747, C274, $D$2:$D$747, D274, $E$2:$E$747, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="10"/>
       <c r="P274" s="10"/>
     </row>
-    <row r="275" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="11">
         <v>46252.6875</v>
       </c>
@@ -13418,7 +13408,7 @@
         <v>118</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B275, $C$2:$C$747, C275, $D$2:$D$747, D275, $E$2:$E$747, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13464,12 +13454,12 @@
         <v>250</v>
       </c>
       <c r="N276" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B276, $C$2:$C$747, C276, $D$2:$D$747, D276, $E$2:$E$747, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P276" s="31"/>
     </row>
-    <row r="277" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="8" t="s">
         <v>62</v>
       </c>
@@ -13499,11 +13489,11 @@
       </c>
       <c r="J277" s="36"/>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B277, $C$2:$C$747, C277, $D$2:$D$747, D277, $E$2:$E$747, E277) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="8" t="s">
         <v>62</v>
       </c>
@@ -13533,11 +13523,11 @@
       </c>
       <c r="J278" s="36"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B278, $C$2:$C$747, C278, $D$2:$D$747, D278, $E$2:$E$747, E278) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="8" t="s">
         <v>62</v>
       </c>
@@ -13567,12 +13557,12 @@
       </c>
       <c r="J279" s="36"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B279, $C$2:$C$747, C279, $D$2:$D$747, D279, $E$2:$E$747, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P279" s="31"/>
     </row>
-    <row r="280" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="8" t="s">
         <v>62</v>
       </c>
@@ -13604,11 +13594,11 @@
         <v>118</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B280, $C$2:$C$747, C280, $D$2:$D$747, D280, $E$2:$E$747, E280) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="8" t="s">
         <v>62</v>
       </c>
@@ -13638,11 +13628,11 @@
       </c>
       <c r="J281" s="36"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B281, $C$2:$C$747, C281, $D$2:$D$747, D281, $E$2:$E$747, E281) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="8" t="s">
         <v>62</v>
       </c>
@@ -13674,11 +13664,11 @@
         <v>117</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B282, $C$2:$C$747, C282, $D$2:$D$747, D282, $E$2:$E$747, E282) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="8" t="s">
         <v>62</v>
       </c>
@@ -13708,12 +13698,12 @@
       </c>
       <c r="J283" s="36"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B283, $C$2:$C$747, C283, $D$2:$D$747, D283, $E$2:$E$747, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O283" s="31"/>
     </row>
-    <row r="284" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="8" t="s">
         <v>62</v>
       </c>
@@ -13743,11 +13733,11 @@
       </c>
       <c r="J284" s="36"/>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B284, $C$2:$C$747, C284, $D$2:$D$747, D284, $E$2:$E$747, E284) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="11">
         <v>46252.6875</v>
       </c>
@@ -13779,11 +13769,11 @@
         <v>118</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B285, $C$2:$C$747, C285, $D$2:$D$747, D285, $E$2:$E$747, E285) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="8" t="s">
         <v>62</v>
       </c>
@@ -13818,13 +13808,13 @@
       <c r="L286" s="18"/>
       <c r="M286" s="18"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B286, $C$2:$C$747, C286, $D$2:$D$747, D286, $E$2:$E$747, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O286" s="10"/>
       <c r="P286" s="10"/>
     </row>
-    <row r="287" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="11">
         <v>46252.6875</v>
       </c>
@@ -13856,11 +13846,11 @@
         <v>118</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B287, $C$2:$C$747, C287, $D$2:$D$747, D287, $E$2:$E$747, E287) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="8" t="s">
         <v>62</v>
       </c>
@@ -13890,11 +13880,11 @@
       </c>
       <c r="J288" s="36"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B288, $C$2:$C$747, C288, $D$2:$D$747, D288, $E$2:$E$747, E288) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -13936,11 +13926,11 @@
         <v>300</v>
       </c>
       <c r="N289" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B289, $C$2:$C$747, C289, $D$2:$D$747, D289, $E$2:$E$747, E289) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="8" t="s">
         <v>62</v>
       </c>
@@ -13975,13 +13965,13 @@
       <c r="L290" s="18"/>
       <c r="M290" s="18"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B290, $C$2:$C$747, C290, $D$2:$D$747, D290, $E$2:$E$747, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O290" s="10"/>
       <c r="P290" s="10"/>
     </row>
-    <row r="291" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="8" t="s">
         <v>62</v>
       </c>
@@ -14011,11 +14001,11 @@
       </c>
       <c r="J291" s="36"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B291, $C$2:$C$747, C291, $D$2:$D$747, D291, $E$2:$E$747, E291) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -14047,11 +14037,11 @@
         <v>55</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B292, $C$2:$C$747, C292, $D$2:$D$747, D292, $E$2:$E$747, E292) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="293" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="8" t="s">
         <v>62</v>
       </c>
@@ -14081,11 +14071,11 @@
       </c>
       <c r="J293" s="36"/>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B293, $C$2:$C$747, C293, $D$2:$D$747, D293, $E$2:$E$747, E293) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="294" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -14127,11 +14117,11 @@
         <v>250</v>
       </c>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B294, $C$2:$C$747, C294, $D$2:$D$747, D294, $E$2:$E$747, E294) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="295" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="8" t="s">
         <v>62</v>
       </c>
@@ -14161,11 +14151,11 @@
       </c>
       <c r="J295" s="36"/>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B295, $C$2:$C$747, C295, $D$2:$D$747, D295, $E$2:$E$747, E295) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="296" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="13"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="11">
         <v>46251.506249999999</v>
       </c>
@@ -14195,12 +14185,12 @@
       </c>
       <c r="J296" s="36"/>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B296, $C$2:$C$747, C296, $D$2:$D$747, D296, $E$2:$E$747, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O296" s="31"/>
     </row>
-    <row r="297" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="8" t="s">
         <v>62</v>
       </c>
@@ -14230,20 +14220,17 @@
       </c>
       <c r="J297" s="36"/>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$747, B297, $C$2:$C$747, C297, $D$2:$D$747, D297, $E$2:$E$747, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P297" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="S"/>
+        <filter val="ARE&amp;MEQ"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P297">
-      <sortCondition ref="F1"/>
-    </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14624,7 +14611,7 @@
         <v>10680</v>
       </c>
       <c r="N2" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B2, $C$2:$C$748, C2, $D$2:$D$748, D2, $E$2:$E$748, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$748, B2, $C$2:$C$748, C2, $D$2:$D$748, D2, $E$2:$E$748, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -14672,7 +14659,7 @@
         <v>10880</v>
       </c>
       <c r="N3" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B3, $C$2:$C$748, C3, $D$2:$D$748, D3, $E$2:$E$748, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -14713,7 +14700,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B4, $C$2:$C$748, C4, $D$2:$D$748, D4, $E$2:$E$748, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -14754,7 +14741,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B5, $C$2:$C$748, C5, $D$2:$D$748, D5, $E$2:$E$748, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -14795,7 +14782,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B6, $C$2:$C$748, C6, $D$2:$D$748, D6, $E$2:$E$748, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -14836,7 +14823,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B7, $C$2:$C$748, C7, $D$2:$D$748, D7, $E$2:$E$748, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14875,7 +14862,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B8, $C$2:$C$748, C8, $D$2:$D$748, D8, $E$2:$E$748, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
@@ -14923,7 +14910,7 @@
         <v>300</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B9, $C$2:$C$748, C9, $D$2:$D$748, D9, $E$2:$E$748, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O9" s="10"/>
@@ -14962,7 +14949,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B10, $C$2:$C$748, C10, $D$2:$D$748, D10, $E$2:$E$748, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="26"/>
@@ -15010,7 +14997,7 @@
         <v>300</v>
       </c>
       <c r="N11" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B11, $C$2:$C$748, C11, $D$2:$D$748, D11, $E$2:$E$748, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
@@ -15058,7 +15045,7 @@
         <v>34175</v>
       </c>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B12, $C$2:$C$748, C12, $D$2:$D$748, D12, $E$2:$E$748, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -15099,7 +15086,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B13, $C$2:$C$748, C13, $D$2:$D$748, D13, $E$2:$E$748, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -15140,7 +15127,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B14, $C$2:$C$748, C14, $D$2:$D$748, D14, $E$2:$E$748, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15177,7 +15164,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B15, $C$2:$C$748, C15, $D$2:$D$748, D15, $E$2:$E$748, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="19"/>
@@ -15221,7 +15208,7 @@
         <v>3156</v>
       </c>
       <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B16, $C$2:$C$748, C16, $D$2:$D$748, D16, $E$2:$E$748, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="10"/>
@@ -15260,7 +15247,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B17, $C$2:$C$748, C17, $D$2:$D$748, D17, $E$2:$E$748, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15299,7 +15286,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B18, $C$2:$C$748, C18, $D$2:$D$748, D18, $E$2:$E$748, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15336,7 +15323,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B19, $C$2:$C$748, C19, $D$2:$D$748, D19, $E$2:$E$748, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="10"/>
@@ -15375,7 +15362,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B20, $C$2:$C$748, C20, $D$2:$D$748, D20, $E$2:$E$748, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="10"/>
@@ -15416,7 +15403,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B21, $C$2:$C$748, C21, $D$2:$D$748, D21, $E$2:$E$748, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="10"/>
@@ -15463,7 +15450,7 @@
         <v>460</v>
       </c>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B22, $C$2:$C$748, C22, $D$2:$D$748, D22, $E$2:$E$748, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P22" s="10"/>
@@ -15503,7 +15490,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B23, $C$2:$C$748, C23, $D$2:$D$748, D23, $E$2:$E$748, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15542,7 +15529,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B24, $C$2:$C$748, C24, $D$2:$D$748, D24, $E$2:$E$748, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="10"/>
@@ -15583,7 +15570,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B25, $C$2:$C$748, C25, $D$2:$D$748, D25, $E$2:$E$748, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15630,7 +15617,7 @@
         <v>540</v>
       </c>
       <c r="N26" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B26, $C$2:$C$748, C26, $D$2:$D$748, D26, $E$2:$E$748, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -15669,7 +15656,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B27, $C$2:$C$748, C27, $D$2:$D$748, D27, $E$2:$E$748, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27"/>
@@ -15707,7 +15694,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B28, $C$2:$C$748, C28, $D$2:$D$748, D28, $E$2:$E$748, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -15748,7 +15735,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B29, $C$2:$C$748, C29, $D$2:$D$748, D29, $E$2:$E$748, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -15796,7 +15783,7 @@
         <v>300</v>
       </c>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B30, $C$2:$C$748, C30, $D$2:$D$748, D30, $E$2:$E$748, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15842,7 +15829,7 @@
         <v>525</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B31, $C$2:$C$748, C31, $D$2:$D$748, D31, $E$2:$E$748, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15888,7 +15875,7 @@
         <v>500</v>
       </c>
       <c r="N32" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B32, $C$2:$C$748, C32, $D$2:$D$748, D32, $E$2:$E$748, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -15927,7 +15914,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B33, $C$2:$C$748, C33, $D$2:$D$748, D33, $E$2:$E$748, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -15968,7 +15955,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B34, $C$2:$C$748, C34, $D$2:$D$748, D34, $E$2:$E$748, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16005,7 +15992,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B35, $C$2:$C$748, C35, $D$2:$D$748, D35, $E$2:$E$748, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -16046,7 +16033,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B36, $C$2:$C$748, C36, $D$2:$D$748, D36, $E$2:$E$748, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="10"/>
@@ -16085,7 +16072,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B37, $C$2:$C$748, C37, $D$2:$D$748, D37, $E$2:$E$748, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -16126,7 +16113,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B38, $C$2:$C$748, C38, $D$2:$D$748, D38, $E$2:$E$748, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -16167,7 +16154,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B39, $C$2:$C$748, C39, $D$2:$D$748, D39, $E$2:$E$748, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -16208,7 +16195,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B40, $C$2:$C$748, C40, $D$2:$D$748, D40, $E$2:$E$748, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -16246,7 +16233,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B41, $C$2:$C$748, C41, $D$2:$D$748, D41, $E$2:$E$748, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -16287,7 +16274,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B42, $C$2:$C$748, C42, $D$2:$D$748, D42, $E$2:$E$748, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -16328,7 +16315,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B43, $C$2:$C$748, C43, $D$2:$D$748, D43, $E$2:$E$748, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43" s="30"/>
@@ -16369,7 +16356,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B44, $C$2:$C$748, C44, $D$2:$D$748, D44, $E$2:$E$748, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -16408,7 +16395,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B45, $C$2:$C$748, C45, $D$2:$D$748, D45, $E$2:$E$748, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -16447,7 +16434,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B46, $C$2:$C$748, C46, $D$2:$D$748, D46, $E$2:$E$748, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -16485,7 +16472,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B47, $C$2:$C$748, C47, $D$2:$D$748, D47, $E$2:$E$748, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -16533,7 +16520,7 @@
         <v>300</v>
       </c>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B48, $C$2:$C$748, C48, $D$2:$D$748, D48, $E$2:$E$748, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -16574,7 +16561,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B49, $C$2:$C$748, C49, $D$2:$D$748, D49, $E$2:$E$748, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -16613,7 +16600,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B50, $C$2:$C$748, C50, $D$2:$D$748, D50, $E$2:$E$748, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -16654,7 +16641,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B51, $C$2:$C$748, C51, $D$2:$D$748, D51, $E$2:$E$748, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -16697,7 +16684,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B52, $C$2:$C$748, C52, $D$2:$D$748, D52, $E$2:$E$748, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -16736,7 +16723,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B53, $C$2:$C$748, C53, $D$2:$D$748, D53, $E$2:$E$748, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -16775,7 +16762,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B54, $C$2:$C$748, C54, $D$2:$D$748, D54, $E$2:$E$748, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -16814,7 +16801,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B55, $C$2:$C$748, C55, $D$2:$D$748, D55, $E$2:$E$748, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -16853,7 +16840,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B56, $C$2:$C$748, C56, $D$2:$D$748, D56, $E$2:$E$748, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -16901,7 +16888,7 @@
         <v>26810</v>
       </c>
       <c r="N57" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B57, $C$2:$C$748, C57, $D$2:$D$748, D57, $E$2:$E$748, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16940,7 +16927,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B58, $C$2:$C$748, C58, $D$2:$D$748, D58, $E$2:$E$748, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -16979,7 +16966,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B59, $C$2:$C$748, C59, $D$2:$D$748, D59, $E$2:$E$748, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -17027,7 +17014,7 @@
         <v>26710</v>
       </c>
       <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B60, $C$2:$C$748, C60, $D$2:$D$748, D60, $E$2:$E$748, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="41" t="s">
@@ -17067,7 +17054,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B61, $C$2:$C$748, C61, $D$2:$D$748, D61, $E$2:$E$748, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -17106,7 +17093,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B62, $C$2:$C$748, C62, $D$2:$D$748, D62, $E$2:$E$748, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
@@ -17147,7 +17134,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B63, $C$2:$C$748, C63, $D$2:$D$748, D63, $E$2:$E$748, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -17186,7 +17173,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B64, $C$2:$C$748, C64, $D$2:$D$748, D64, $E$2:$E$748, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -17230,11 +17217,11 @@
         <v>13052</v>
       </c>
       <c r="M65" s="18">
-        <f t="shared" ref="M65:M70" si="0">ABS((D65*E65)-L65)</f>
+        <f t="shared" ref="M65:M70" si="1">ABS((D65*E65)-L65)</f>
         <v>646</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B65, $C$2:$C$748, C65, $D$2:$D$748, D65, $E$2:$E$748, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65" s="10"/>
@@ -17278,11 +17265,11 @@
         <v>3560</v>
       </c>
       <c r="M66" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>175</v>
       </c>
       <c r="N66" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B66, $C$2:$C$748, C66, $D$2:$D$748, D66, $E$2:$E$748, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="2">IF(COUNTIFS( $B$2:$B$748, B66, $C$2:$C$748, C66, $D$2:$D$748, D66, $E$2:$E$748, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O66" s="41" t="s">
@@ -17328,11 +17315,11 @@
         <v>3510</v>
       </c>
       <c r="M67" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>225</v>
       </c>
       <c r="N67" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B67, $C$2:$C$748, C67, $D$2:$D$748, D67, $E$2:$E$748, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O67" s="41" t="s">
@@ -17377,11 +17364,11 @@
         <v>35880</v>
       </c>
       <c r="M68" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26610</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B68, $C$2:$C$748, C68, $D$2:$D$748, D68, $E$2:$E$748, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17423,11 +17410,11 @@
         <v>8400</v>
       </c>
       <c r="M69" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B69, $C$2:$C$748, C69, $D$2:$D$748, D69, $E$2:$E$748, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17469,11 +17456,11 @@
         <v>17404</v>
       </c>
       <c r="M70" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>516</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B70, $C$2:$C$748, C70, $D$2:$D$748, D70, $E$2:$E$748, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O70" s="10"/>
@@ -17512,7 +17499,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B71, $C$2:$C$748, C71, $D$2:$D$748, D71, $E$2:$E$748, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17549,7 +17536,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B72, $C$2:$C$748, C72, $D$2:$D$748, D72, $E$2:$E$748, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17591,11 +17578,11 @@
         <v>16219.999999999998</v>
       </c>
       <c r="M73" s="29">
-        <f t="shared" ref="M73:M85" si="1">ABS((D73*E73)-L73)</f>
+        <f t="shared" ref="M73:M85" si="3">ABS((D73*E73)-L73)</f>
         <v>300.00000000000182</v>
       </c>
       <c r="N73" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B73, $C$2:$C$748, C73, $D$2:$D$748, D73, $E$2:$E$748, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="41" t="s">
@@ -17641,11 +17628,11 @@
         <v>6334</v>
       </c>
       <c r="M74" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>274</v>
       </c>
       <c r="N74" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B74, $C$2:$C$748, C74, $D$2:$D$748, D74, $E$2:$E$748, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="41" t="s">
@@ -17691,11 +17678,11 @@
         <v>4640</v>
       </c>
       <c r="M75" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B75, $C$2:$C$748, C75, $D$2:$D$748, D75, $E$2:$E$748, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="10"/>
@@ -17739,11 +17726,11 @@
         <v>9170</v>
       </c>
       <c r="M76" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B76, $C$2:$C$748, C76, $D$2:$D$748, D76, $E$2:$E$748, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="10"/>
@@ -17787,11 +17774,11 @@
         <v>39300</v>
       </c>
       <c r="M77" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>18850</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B77, $C$2:$C$748, C77, $D$2:$D$748, D77, $E$2:$E$748, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="10"/>
@@ -17835,11 +17822,11 @@
         <v>19300</v>
       </c>
       <c r="M78" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B78, $C$2:$C$748, C78, $D$2:$D$748, D78, $E$2:$E$748, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17881,11 +17868,11 @@
         <v>14440</v>
       </c>
       <c r="M79" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B79, $C$2:$C$748, C79, $D$2:$D$748, D79, $E$2:$E$748, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O79"/>
@@ -17929,11 +17916,11 @@
         <v>8220</v>
       </c>
       <c r="M80" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>360</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B80, $C$2:$C$748, C80, $D$2:$D$748, D80, $E$2:$E$748, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="41" t="s">
@@ -17979,11 +17966,11 @@
         <v>35880</v>
       </c>
       <c r="M81" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>26460</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B81, $C$2:$C$748, C81, $D$2:$D$748, D81, $E$2:$E$748, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="10"/>
@@ -18027,11 +18014,11 @@
         <v>19730.5</v>
       </c>
       <c r="M82" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>504.5</v>
       </c>
       <c r="N82" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B82, $C$2:$C$748, C82, $D$2:$D$748, D82, $E$2:$E$748, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O82" s="41" t="s">
@@ -18076,11 +18063,11 @@
         <v>19690</v>
       </c>
       <c r="M83" s="29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>545</v>
       </c>
       <c r="N83" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B83, $C$2:$C$748, C83, $D$2:$D$748, D83, $E$2:$E$748, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O83" s="41" t="s">
@@ -18126,11 +18113,11 @@
         <v>15075</v>
       </c>
       <c r="M84" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>645</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B84, $C$2:$C$748, C84, $D$2:$D$748, D84, $E$2:$E$748, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="41" t="s">
@@ -18176,11 +18163,11 @@
         <v>3300</v>
       </c>
       <c r="M85" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B85, $C$2:$C$748, C85, $D$2:$D$748, D85, $E$2:$E$748, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="10"/>
@@ -18216,7 +18203,7 @@
       </c>
       <c r="J86" s="36"/>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B86, $C$2:$C$748, C86, $D$2:$D$748, D86, $E$2:$E$748, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18262,7 +18249,7 @@
         <v>810</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B87, $C$2:$C$748, C87, $D$2:$D$748, D87, $E$2:$E$748, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18308,7 +18295,7 @@
         <v>1200</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B88, $C$2:$C$748, C88, $D$2:$D$748, D88, $E$2:$E$748, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18354,7 +18341,7 @@
         <v>300</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B89, $C$2:$C$748, C89, $D$2:$D$748, D89, $E$2:$E$748, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18391,7 +18378,7 @@
       <c r="L90" s="17"/>
       <c r="M90" s="17"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B90, $C$2:$C$748, C90, $D$2:$D$748, D90, $E$2:$E$748, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O90"/>
@@ -18435,11 +18422,11 @@
         <v>2899.25</v>
       </c>
       <c r="M91" s="18">
-        <f t="shared" ref="M91:M99" si="2">ABS((D91*E91)-L91)</f>
+        <f t="shared" ref="M91:M99" si="4">ABS((D91*E91)-L91)</f>
         <v>300.75</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B91, $C$2:$C$748, C91, $D$2:$D$748, D91, $E$2:$E$748, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="10"/>
@@ -18483,11 +18470,11 @@
         <v>16580</v>
       </c>
       <c r="M92" s="47">
+        <f t="shared" si="4"/>
+        <v>750</v>
+      </c>
+      <c r="N92" s="25" t="str">
         <f t="shared" si="2"/>
-        <v>750</v>
-      </c>
-      <c r="N92" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B92, $C$2:$C$748, C92, $D$2:$D$748, D92, $E$2:$E$748, E92) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O92" s="25"/>
@@ -18533,11 +18520,11 @@
         <v>5585</v>
       </c>
       <c r="M93" s="29">
+        <f t="shared" si="4"/>
+        <v>395</v>
+      </c>
+      <c r="N93" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>395</v>
-      </c>
-      <c r="N93" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B93, $C$2:$C$748, C93, $D$2:$D$748, D93, $E$2:$E$748, E93) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O93" s="31"/>
@@ -18581,11 +18568,11 @@
         <v>5730</v>
       </c>
       <c r="M94" s="29">
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="N94" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="N94" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B94, $C$2:$C$748, C94, $D$2:$D$748, D94, $E$2:$E$748, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O94" s="31"/>
@@ -18629,11 +18616,11 @@
         <v>20010</v>
       </c>
       <c r="M95" s="18">
+        <f t="shared" si="4"/>
+        <v>450</v>
+      </c>
+      <c r="N95" t="str">
         <f t="shared" si="2"/>
-        <v>450</v>
-      </c>
-      <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B95, $C$2:$C$748, C95, $D$2:$D$748, D95, $E$2:$E$748, E95) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P95"/>
@@ -18676,11 +18663,11 @@
         <v>10300</v>
       </c>
       <c r="M96" s="18">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="N96" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B96, $C$2:$C$748, C96, $D$2:$D$748, D96, $E$2:$E$748, E96) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P96" s="31"/>
@@ -18723,11 +18710,11 @@
         <v>16500</v>
       </c>
       <c r="M97" s="18">
+        <f t="shared" si="4"/>
+        <v>1400</v>
+      </c>
+      <c r="N97" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>1400</v>
-      </c>
-      <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B97, $C$2:$C$748, C97, $D$2:$D$748, D97, $E$2:$E$748, E97) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O97" s="10"/>
@@ -18771,11 +18758,11 @@
         <v>23450</v>
       </c>
       <c r="M98" s="18">
+        <f t="shared" si="4"/>
+        <v>1500</v>
+      </c>
+      <c r="N98" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>1500</v>
-      </c>
-      <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B98, $C$2:$C$748, C98, $D$2:$D$748, D98, $E$2:$E$748, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O98" s="10"/>
@@ -18819,11 +18806,11 @@
         <v>8420</v>
       </c>
       <c r="M99" s="18">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="N99" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B99, $C$2:$C$748, C99, $D$2:$D$748, D99, $E$2:$E$748, E99) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -18859,7 +18846,7 @@
         <v>117</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B100, $C$2:$C$748, C100, $D$2:$D$748, D100, $E$2:$E$748, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18905,7 +18892,7 @@
         <v>300</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B101, $C$2:$C$748, C101, $D$2:$D$748, D101, $E$2:$E$748, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P101" s="19"/>
@@ -18942,7 +18929,7 @@
         <v>118</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B102, $C$2:$C$748, C102, $D$2:$D$748, D102, $E$2:$E$748, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="41" t="s">
@@ -18982,7 +18969,7 @@
         <v>118</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B103, $C$2:$C$748, C103, $D$2:$D$748, D103, $E$2:$E$748, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19024,11 +19011,11 @@
         <v>20260</v>
       </c>
       <c r="M104" s="18">
-        <f t="shared" ref="M104:M113" si="3">ABS((D104*E104)-L104)</f>
+        <f t="shared" ref="M104:M113" si="5">ABS((D104*E104)-L104)</f>
         <v>300</v>
       </c>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B104, $C$2:$C$748, C104, $D$2:$D$748, D104, $E$2:$E$748, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O104"/>
@@ -19072,11 +19059,11 @@
         <v>10400</v>
       </c>
       <c r="M105" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B105, $C$2:$C$748, C105, $D$2:$D$748, D105, $E$2:$E$748, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19118,11 +19105,11 @@
         <v>32900</v>
       </c>
       <c r="M106" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="N106" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B106, $C$2:$C$748, C106, $D$2:$D$748, D106, $E$2:$E$748, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O106" s="26"/>
@@ -19165,11 +19152,11 @@
         <v>33200</v>
       </c>
       <c r="M107" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>700</v>
       </c>
       <c r="N107" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B107, $C$2:$C$748, C107, $D$2:$D$748, D107, $E$2:$E$748, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -19211,11 +19198,11 @@
         <v>4410</v>
       </c>
       <c r="M108" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>580</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B108, $C$2:$C$748, C108, $D$2:$D$748, D108, $E$2:$E$748, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19257,11 +19244,11 @@
         <v>39300</v>
       </c>
       <c r="M109" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18350</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B109, $C$2:$C$748, C109, $D$2:$D$748, D109, $E$2:$E$748, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="10"/>
@@ -19305,11 +19292,11 @@
         <v>5755</v>
       </c>
       <c r="M110" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>275</v>
       </c>
       <c r="N110" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B110, $C$2:$C$748, C110, $D$2:$D$748, D110, $E$2:$E$748, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O110" s="41" t="s">
@@ -19354,11 +19341,11 @@
         <v>5805</v>
       </c>
       <c r="M111" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>225</v>
       </c>
       <c r="N111" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B111, $C$2:$C$748, C111, $D$2:$D$748, D111, $E$2:$E$748, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O111" s="41" t="s">
@@ -19403,11 +19390,11 @@
         <v>11320</v>
       </c>
       <c r="M112" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B112, $C$2:$C$748, C112, $D$2:$D$748, D112, $E$2:$E$748, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19449,11 +19436,11 @@
         <v>4852</v>
       </c>
       <c r="M113" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B113, $C$2:$C$748, C113, $D$2:$D$748, D113, $E$2:$E$748, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19487,7 +19474,7 @@
       </c>
       <c r="J114" s="36"/>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B114, $C$2:$C$748, C114, $D$2:$D$748, D114, $E$2:$E$748, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19529,11 +19516,11 @@
         <v>3005</v>
       </c>
       <c r="M115" s="18">
-        <f t="shared" ref="M115:M120" si="4">ABS((D115*E115)-L115)</f>
+        <f t="shared" ref="M115:M120" si="6">ABS((D115*E115)-L115)</f>
         <v>240</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B115, $C$2:$C$748, C115, $D$2:$D$748, D115, $E$2:$E$748, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P115" s="26"/>
@@ -19576,11 +19563,11 @@
         <v>8700</v>
       </c>
       <c r="M116" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B116, $C$2:$C$748, C116, $D$2:$D$748, D116, $E$2:$E$748, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
@@ -19624,11 +19611,11 @@
         <v>10410</v>
       </c>
       <c r="M117" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B117, $C$2:$C$748, C117, $D$2:$D$748, D117, $E$2:$E$748, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="P117" s="10"/>
@@ -19671,11 +19658,11 @@
         <v>16755</v>
       </c>
       <c r="M118" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>295</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B118, $C$2:$C$748, C118, $D$2:$D$748, D118, $E$2:$E$748, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="10"/>
@@ -19719,11 +19706,11 @@
         <v>17040</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>880</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B119, $C$2:$C$748, C119, $D$2:$D$748, D119, $E$2:$E$748, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="41" t="s">
@@ -19768,11 +19755,11 @@
         <v>3400</v>
       </c>
       <c r="M120" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B120, $C$2:$C$748, C120, $D$2:$D$748, D120, $E$2:$E$748, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19806,7 +19793,7 @@
       </c>
       <c r="J121" s="36"/>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B121, $C$2:$C$748, C121, $D$2:$D$748, D121, $E$2:$E$748, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="41" t="s">
@@ -19844,7 +19831,7 @@
       </c>
       <c r="J122" s="36"/>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B122, $C$2:$C$748, C122, $D$2:$D$748, D122, $E$2:$E$748, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="25"/>
@@ -19887,11 +19874,11 @@
         <v>10510</v>
       </c>
       <c r="M123" s="18">
-        <f t="shared" ref="M123:M129" si="5">ABS((D123*E123)-L123)</f>
+        <f t="shared" ref="M123:M129" si="7">ABS((D123*E123)-L123)</f>
         <v>300</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B123, $C$2:$C$748, C123, $D$2:$D$748, D123, $E$2:$E$748, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19933,11 +19920,11 @@
         <v>18800</v>
       </c>
       <c r="M124" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B124, $C$2:$C$748, C124, $D$2:$D$748, D124, $E$2:$E$748, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="42" t="s">
@@ -19982,11 +19969,11 @@
         <v>33950</v>
       </c>
       <c r="M125" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>480</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B125, $C$2:$C$748, C125, $D$2:$D$748, D125, $E$2:$E$748, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20028,11 +20015,11 @@
         <v>8320</v>
       </c>
       <c r="M126" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>650</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B126, $C$2:$C$748, C126, $D$2:$D$748, D126, $E$2:$E$748, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20074,11 +20061,11 @@
         <v>3810</v>
       </c>
       <c r="M127" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N127" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B127, $C$2:$C$748, C127, $D$2:$D$748, D127, $E$2:$E$748, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20120,11 +20107,11 @@
         <v>9470</v>
       </c>
       <c r="M128" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B128, $C$2:$C$748, C128, $D$2:$D$748, D128, $E$2:$E$748, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20166,11 +20153,11 @@
         <v>10249</v>
       </c>
       <c r="M129" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4451</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B129, $C$2:$C$748, C129, $D$2:$D$748, D129, $E$2:$E$748, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="10"/>
@@ -20206,7 +20193,7 @@
       </c>
       <c r="J130" s="36"/>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B130, $C$2:$C$748, C130, $D$2:$D$748, D130, $E$2:$E$748, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="8">IF(COUNTIFS( $B$2:$B$748, B130, $C$2:$C$748, C130, $D$2:$D$748, D130, $E$2:$E$748, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -20248,11 +20235,11 @@
         <v>73800</v>
       </c>
       <c r="M131" s="18">
-        <f t="shared" ref="M131:M146" si="6">ABS((D131*E131)-L131)</f>
+        <f t="shared" ref="M131:M146" si="9">ABS((D131*E131)-L131)</f>
         <v>48320</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B131, $C$2:$C$748, C131, $D$2:$D$748, D131, $E$2:$E$748, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="41" t="s">
@@ -20297,11 +20284,11 @@
         <v>7578</v>
       </c>
       <c r="M132" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>294</v>
       </c>
       <c r="N132" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B132, $C$2:$C$748, C132, $D$2:$D$748, D132, $E$2:$E$748, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20343,11 +20330,11 @@
         <v>7578</v>
       </c>
       <c r="M133" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>294</v>
       </c>
       <c r="N133" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B133, $C$2:$C$748, C133, $D$2:$D$748, D133, $E$2:$E$748, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20389,11 +20376,11 @@
         <v>4968</v>
       </c>
       <c r="M134" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>280</v>
       </c>
       <c r="N134" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B134, $C$2:$C$748, C134, $D$2:$D$748, D134, $E$2:$E$748, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20435,11 +20422,11 @@
         <v>4680</v>
       </c>
       <c r="M135" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>140</v>
       </c>
       <c r="N135" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B135, $C$2:$C$748, C135, $D$2:$D$748, D135, $E$2:$E$748, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
       <c r="P135" s="31"/>
@@ -20482,11 +20469,11 @@
         <v>4520</v>
       </c>
       <c r="M136" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N136" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B136, $C$2:$C$748, C136, $D$2:$D$748, D136, $E$2:$E$748, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -20528,11 +20515,11 @@
         <v>8480</v>
       </c>
       <c r="M137" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>280</v>
       </c>
       <c r="N137" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B137, $C$2:$C$748, C137, $D$2:$D$748, D137, $E$2:$E$748, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="41" t="s">
@@ -20577,11 +20564,11 @@
         <v>11660</v>
       </c>
       <c r="M138" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B138, $C$2:$C$748, C138, $D$2:$D$748, D138, $E$2:$E$748, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="41" t="s">
@@ -20626,11 +20613,11 @@
         <v>5905</v>
       </c>
       <c r="M139" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>275</v>
       </c>
       <c r="N139" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B139, $C$2:$C$748, C139, $D$2:$D$748, D139, $E$2:$E$748, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20672,11 +20659,11 @@
         <v>34100</v>
       </c>
       <c r="M140" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>700</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B140, $C$2:$C$748, C140, $D$2:$D$748, D140, $E$2:$E$748, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="31"/>
@@ -20719,11 +20706,11 @@
         <v>14100</v>
       </c>
       <c r="M141" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>500</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B141, $C$2:$C$748, C141, $D$2:$D$748, D141, $E$2:$E$748, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20765,11 +20752,11 @@
         <v>5370</v>
       </c>
       <c r="M142" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>320</v>
       </c>
       <c r="N142" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B142, $C$2:$C$748, C142, $D$2:$D$748, D142, $E$2:$E$748, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="31"/>
@@ -20813,11 +20800,11 @@
         <v>2610</v>
       </c>
       <c r="M143" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>235</v>
       </c>
       <c r="N143" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B143, $C$2:$C$748, C143, $D$2:$D$748, D143, $E$2:$E$748, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="31"/>
@@ -20861,11 +20848,11 @@
         <v>17150</v>
       </c>
       <c r="M144" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B144, $C$2:$C$748, C144, $D$2:$D$748, D144, $E$2:$E$748, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20907,11 +20894,11 @@
         <v>4120</v>
       </c>
       <c r="M145" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>270</v>
       </c>
       <c r="N145" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B145, $C$2:$C$748, C145, $D$2:$D$748, D145, $E$2:$E$748, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="30" t="s">
@@ -20956,11 +20943,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M146" s="29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N146" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B146, $C$2:$C$748, C146, $D$2:$D$748, D146, $E$2:$E$748, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="30" t="s">
@@ -21003,7 +20990,7 @@
       <c r="L147" s="18"/>
       <c r="M147" s="18"/>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B147, $C$2:$C$748, C147, $D$2:$D$748, D147, $E$2:$E$748, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O147" s="10"/>
@@ -21044,7 +21031,7 @@
       <c r="L148" s="18"/>
       <c r="M148" s="18"/>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B148, $C$2:$C$748, C148, $D$2:$D$748, D148, $E$2:$E$748, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P148" s="10"/>
@@ -21091,7 +21078,7 @@
         <v>710.99999999999636</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B149, $C$2:$C$748, C149, $D$2:$D$748, D149, $E$2:$E$748, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="41" t="s">
@@ -21141,7 +21128,7 @@
         <v>800</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B150, $C$2:$C$748, C150, $D$2:$D$748, D150, $E$2:$E$748, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21187,7 +21174,7 @@
         <v>816</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B151, $C$2:$C$748, C151, $D$2:$D$748, D151, $E$2:$E$748, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21233,7 +21220,7 @@
         <v>500</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B152, $C$2:$C$748, C152, $D$2:$D$748, D152, $E$2:$E$748, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21279,7 +21266,7 @@
         <v>47900</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B153, $C$2:$C$748, C153, $D$2:$D$748, D153, $E$2:$E$748, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="41" t="s">
@@ -21318,7 +21305,7 @@
         <v>196</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B154, $C$2:$C$748, C154, $D$2:$D$748, D154, $E$2:$E$748, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21364,7 +21351,7 @@
         <v>150</v>
       </c>
       <c r="N155" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B155, $C$2:$C$748, C155, $D$2:$D$748, D155, $E$2:$E$748, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -21410,7 +21397,7 @@
         <v>250</v>
       </c>
       <c r="N156" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B156, $C$2:$C$748, C156, $D$2:$D$748, D156, $E$2:$E$748, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -21446,7 +21433,7 @@
         <v>117</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B157, $C$2:$C$748, C157, $D$2:$D$748, D157, $E$2:$E$748, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21492,7 +21479,7 @@
         <v>650</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B158, $C$2:$C$748, C158, $D$2:$D$748, D158, $E$2:$E$748, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O158" s="41" t="s">
@@ -21541,7 +21528,7 @@
         <v>495</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B159, $C$2:$C$748, C159, $D$2:$D$748, D159, $E$2:$E$748, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="41" t="s">
@@ -21581,7 +21568,7 @@
       <c r="L160" s="18"/>
       <c r="M160" s="18"/>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B160, $C$2:$C$748, C160, $D$2:$D$748, D160, $E$2:$E$748, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="10"/>
@@ -21620,7 +21607,7 @@
       <c r="L161" s="18"/>
       <c r="M161" s="18"/>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B161, $C$2:$C$748, C161, $D$2:$D$748, D161, $E$2:$E$748, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P161" s="10"/>
@@ -21655,7 +21642,7 @@
       </c>
       <c r="J162" s="36"/>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B162, $C$2:$C$748, C162, $D$2:$D$748, D162, $E$2:$E$748, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21689,7 +21676,7 @@
       </c>
       <c r="J163" s="36"/>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B163, $C$2:$C$748, C163, $D$2:$D$748, D163, $E$2:$E$748, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21723,7 +21710,7 @@
       </c>
       <c r="J164" s="21"/>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B164, $C$2:$C$748, C164, $D$2:$D$748, D164, $E$2:$E$748, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21762,7 +21749,7 @@
         <v>145</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B165, $C$2:$C$748, C165, $D$2:$D$748, D165, $E$2:$E$748, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21808,7 +21795,7 @@
         <v>300</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B166, $C$2:$C$748, C166, $D$2:$D$748, D166, $E$2:$E$748, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O166" s="41" t="s">
@@ -21857,7 +21844,7 @@
         <v>651</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B167, $C$2:$C$748, C167, $D$2:$D$748, D167, $E$2:$E$748, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21903,7 +21890,7 @@
         <v>300</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B168, $C$2:$C$748, C168, $D$2:$D$748, D168, $E$2:$E$748, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21949,7 +21936,7 @@
         <v>300</v>
       </c>
       <c r="N169" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B169, $C$2:$C$748, C169, $D$2:$D$748, D169, $E$2:$E$748, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="41" t="s">
@@ -21999,7 +21986,7 @@
         <v>650</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B170, $C$2:$C$748, C170, $D$2:$D$748, D170, $E$2:$E$748, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="41" t="s">
@@ -22038,7 +22025,7 @@
         <v>117</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B171, $C$2:$C$748, C171, $D$2:$D$748, D171, $E$2:$E$748, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22084,7 +22071,7 @@
         <v>260</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B172, $C$2:$C$748, C172, $D$2:$D$748, D172, $E$2:$E$748, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22130,7 +22117,7 @@
         <v>290</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B173, $C$2:$C$748, C173, $D$2:$D$748, D173, $E$2:$E$748, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22176,7 +22163,7 @@
         <v>650</v>
       </c>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B174, $C$2:$C$748, C174, $D$2:$D$748, D174, $E$2:$E$748, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O174"/>
@@ -22224,7 +22211,7 @@
         <v>500</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B175, $C$2:$C$748, C175, $D$2:$D$748, D175, $E$2:$E$748, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22260,7 +22247,7 @@
         <v>118</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B176, $C$2:$C$748, C176, $D$2:$D$748, D176, $E$2:$E$748, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="41" t="s">
@@ -22309,7 +22296,7 @@
         <v>320</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B177, $C$2:$C$748, C177, $D$2:$D$748, D177, $E$2:$E$748, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22355,7 +22342,7 @@
         <v>448</v>
       </c>
       <c r="N178" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B178, $C$2:$C$748, C178, $D$2:$D$748, D178, $E$2:$E$748, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22401,7 +22388,7 @@
         <v>650</v>
       </c>
       <c r="N179" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B179, $C$2:$C$748, C179, $D$2:$D$748, D179, $E$2:$E$748, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="41" t="s">
@@ -22443,7 +22430,7 @@
       <c r="L180" s="18"/>
       <c r="M180" s="18"/>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B180, $C$2:$C$748, C180, $D$2:$D$748, D180, $E$2:$E$748, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="10"/>
@@ -22491,7 +22478,7 @@
         <v>800</v>
       </c>
       <c r="N181" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B181, $C$2:$C$748, C181, $D$2:$D$748, D181, $E$2:$E$748, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22537,7 +22524,7 @@
         <v>250</v>
       </c>
       <c r="N182" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B182, $C$2:$C$748, C182, $D$2:$D$748, D182, $E$2:$E$748, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22571,7 +22558,7 @@
       </c>
       <c r="J183" s="36"/>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B183, $C$2:$C$748, C183, $D$2:$D$748, D183, $E$2:$E$748, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="31"/>
@@ -22618,7 +22605,7 @@
         <v>250</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B184, $C$2:$C$748, C184, $D$2:$D$748, D184, $E$2:$E$748, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P184" s="31"/>
@@ -22665,7 +22652,7 @@
         <v>47480</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B185, $C$2:$C$748, C185, $D$2:$D$748, D185, $E$2:$E$748, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22704,7 +22691,7 @@
         <v>144</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B186, $C$2:$C$748, C186, $D$2:$D$748, D186, $E$2:$E$748, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22740,7 +22727,7 @@
         <v>118</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B187, $C$2:$C$748, C187, $D$2:$D$748, D187, $E$2:$E$748, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22786,7 +22773,7 @@
         <v>340</v>
       </c>
       <c r="N188" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B188, $C$2:$C$748, C188, $D$2:$D$748, D188, $E$2:$E$748, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22822,7 +22809,7 @@
         <v>117</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B189, $C$2:$C$748, C189, $D$2:$D$748, D189, $E$2:$E$748, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22859,7 +22846,7 @@
       <c r="L190" s="18"/>
       <c r="M190" s="18"/>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B190, $C$2:$C$748, C190, $D$2:$D$748, D190, $E$2:$E$748, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="10"/>
@@ -22900,7 +22887,7 @@
       <c r="L191" s="18"/>
       <c r="M191" s="18"/>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B191, $C$2:$C$748, C191, $D$2:$D$748, D191, $E$2:$E$748, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O191" s="10"/>
@@ -22948,7 +22935,7 @@
         <v>300</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B192, $C$2:$C$748, C192, $D$2:$D$748, D192, $E$2:$E$748, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22994,7 +22981,7 @@
         <v>360</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B193, $C$2:$C$748, C193, $D$2:$D$748, D193, $E$2:$E$748, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23040,7 +23027,7 @@
         <v>450</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B194, $C$2:$C$748, C194, $D$2:$D$748, D194, $E$2:$E$748, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="10">IF(COUNTIFS( $B$2:$B$748, B194, $C$2:$C$748, C194, $D$2:$D$748, D194, $E$2:$E$748, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -23076,7 +23063,7 @@
         <v>118</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B195, $C$2:$C$748, C195, $D$2:$D$748, D195, $E$2:$E$748, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23118,11 +23105,11 @@
         <v>10814</v>
       </c>
       <c r="M196" s="18">
-        <f t="shared" ref="M196:M201" si="7">ABS((D196*E196)-L196)</f>
+        <f t="shared" ref="M196:M201" si="11">ABS((D196*E196)-L196)</f>
         <v>501</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B196, $C$2:$C$748, C196, $D$2:$D$748, D196, $E$2:$E$748, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O196" s="41" t="s">
@@ -23167,11 +23154,11 @@
         <v>8800</v>
       </c>
       <c r="M197" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>650</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B197, $C$2:$C$748, C197, $D$2:$D$748, D197, $E$2:$E$748, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O197" s="31"/>
@@ -23214,11 +23201,11 @@
         <v>18140</v>
       </c>
       <c r="M198" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>650</v>
       </c>
       <c r="N198" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B198, $C$2:$C$748, C198, $D$2:$D$748, D198, $E$2:$E$748, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="41" t="s">
@@ -23263,11 +23250,11 @@
         <v>7200</v>
       </c>
       <c r="M199" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>250</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B199, $C$2:$C$748, C199, $D$2:$D$748, D199, $E$2:$E$748, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23309,11 +23296,11 @@
         <v>4170</v>
       </c>
       <c r="M200" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="N200" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B200, $C$2:$C$748, C200, $D$2:$D$748, D200, $E$2:$E$748, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23355,11 +23342,11 @@
         <v>26300</v>
       </c>
       <c r="M201" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B201, $C$2:$C$748, C201, $D$2:$D$748, D201, $E$2:$E$748, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23396,7 +23383,7 @@
       <c r="L202" s="18"/>
       <c r="M202" s="18"/>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B202, $C$2:$C$748, C202, $D$2:$D$748, D202, $E$2:$E$748, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="10"/>
@@ -23434,7 +23421,7 @@
         <v>55</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B203, $C$2:$C$748, C203, $D$2:$D$748, D203, $E$2:$E$748, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23470,7 +23457,7 @@
         <v>118</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B204, $C$2:$C$748, C204, $D$2:$D$748, D204, $E$2:$E$748, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23516,7 +23503,7 @@
         <v>300</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B205, $C$2:$C$748, C205, $D$2:$D$748, D205, $E$2:$E$748, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23555,7 +23542,7 @@
       <c r="L206" s="47"/>
       <c r="M206" s="47"/>
       <c r="N206" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B206, $C$2:$C$748, C206, $D$2:$D$748, D206, $E$2:$E$748, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="25"/>
@@ -23600,7 +23587,7 @@
       <c r="L207" s="17"/>
       <c r="M207" s="17"/>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B207, $C$2:$C$748, C207, $D$2:$D$748, D207, $E$2:$E$748, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="10"/>
@@ -23644,11 +23631,11 @@
         <v>5520</v>
       </c>
       <c r="M208" s="29">
-        <f t="shared" ref="M208:M213" si="8">ABS((D208*E208)-L208)</f>
+        <f t="shared" ref="M208:M213" si="12">ABS((D208*E208)-L208)</f>
         <v>300</v>
       </c>
       <c r="N208" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B208, $C$2:$C$748, C208, $D$2:$D$748, D208, $E$2:$E$748, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="31"/>
@@ -23691,11 +23678,11 @@
         <v>2657</v>
       </c>
       <c r="M209" s="29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>253</v>
       </c>
       <c r="N209" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B209, $C$2:$C$748, C209, $D$2:$D$748, D209, $E$2:$E$748, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Duplicate</v>
       </c>
       <c r="O209" s="31"/>
@@ -23738,11 +23725,11 @@
         <v>2554.5</v>
       </c>
       <c r="M210" s="29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>355.5</v>
       </c>
       <c r="N210" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B210, $C$2:$C$748, C210, $D$2:$D$748, D210, $E$2:$E$748, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Duplicate</v>
       </c>
       <c r="O210" s="31"/>
@@ -23786,11 +23773,11 @@
         <v>5620</v>
       </c>
       <c r="M211" s="29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B211, $C$2:$C$748, C211, $D$2:$D$748, D211, $E$2:$E$748, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P211" s="26"/>
@@ -23833,11 +23820,11 @@
         <v>8820</v>
       </c>
       <c r="M212" s="29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>650</v>
       </c>
       <c r="N212" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B212, $C$2:$C$748, C212, $D$2:$D$748, D212, $E$2:$E$748, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O212" s="31"/>
@@ -23881,11 +23868,11 @@
         <v>36946</v>
       </c>
       <c r="M213" s="29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>934</v>
       </c>
       <c r="N213" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B213, $C$2:$C$748, C213, $D$2:$D$748, D213, $E$2:$E$748, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O213" s="31"/>
@@ -23923,7 +23910,7 @@
         <v>117</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B214, $C$2:$C$748, C214, $D$2:$D$748, D214, $E$2:$E$748, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P214" s="31"/>
@@ -23958,7 +23945,7 @@
       </c>
       <c r="J215" s="36"/>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B215, $C$2:$C$748, C215, $D$2:$D$748, D215, $E$2:$E$748, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P215" s="31"/>
@@ -24005,7 +23992,7 @@
         <v>1800</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B216, $C$2:$C$748, C216, $D$2:$D$748, D216, $E$2:$E$748, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24051,7 +24038,7 @@
         <v>646</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B217, $C$2:$C$748, C217, $D$2:$D$748, D217, $E$2:$E$748, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O217" s="41" t="s">
@@ -24090,7 +24077,7 @@
         <v>118</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B218, $C$2:$C$748, C218, $D$2:$D$748, D218, $E$2:$E$748, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24136,7 +24123,7 @@
         <v>300</v>
       </c>
       <c r="N219" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B219, $C$2:$C$748, C219, $D$2:$D$748, D219, $E$2:$E$748, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O219" s="31"/>
@@ -24184,7 +24171,7 @@
         <v>188</v>
       </c>
       <c r="N220" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B220, $C$2:$C$748, C220, $D$2:$D$748, D220, $E$2:$E$748, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O220" s="31"/>
@@ -24220,7 +24207,7 @@
       </c>
       <c r="J221" s="36"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B221, $C$2:$C$748, C221, $D$2:$D$748, D221, $E$2:$E$748, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24256,7 +24243,7 @@
         <v>154</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B222, $C$2:$C$748, C222, $D$2:$D$748, D222, $E$2:$E$748, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24302,7 +24289,7 @@
         <v>400</v>
       </c>
       <c r="N223" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B223, $C$2:$C$748, C223, $D$2:$D$748, D223, $E$2:$E$748, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24336,7 +24323,7 @@
       </c>
       <c r="J224" s="36"/>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B224, $C$2:$C$748, C224, $D$2:$D$748, D224, $E$2:$E$748, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24382,7 +24369,7 @@
         <v>527.5</v>
       </c>
       <c r="N225" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B225, $C$2:$C$748, C225, $D$2:$D$748, D225, $E$2:$E$748, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O225" s="31"/>
@@ -24425,7 +24412,7 @@
       <c r="L226" s="29"/>
       <c r="M226" s="29"/>
       <c r="N226" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B226, $C$2:$C$748, C226, $D$2:$D$748, D226, $E$2:$E$748, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24461,7 +24448,7 @@
         <v>117</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B227, $C$2:$C$748, C227, $D$2:$D$748, D227, $E$2:$E$748, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24497,7 +24484,7 @@
         <v>117</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B228, $C$2:$C$748, C228, $D$2:$D$748, D228, $E$2:$E$748, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24543,7 +24530,7 @@
         <v>450</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B229, $C$2:$C$748, C229, $D$2:$D$748, D229, $E$2:$E$748, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24579,7 +24566,7 @@
         <v>117</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B230, $C$2:$C$748, C230, $D$2:$D$748, D230, $E$2:$E$748, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24625,7 +24612,7 @@
         <v>1000</v>
       </c>
       <c r="N231" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B231, $C$2:$C$748, C231, $D$2:$D$748, D231, $E$2:$E$748, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P231" s="31"/>
@@ -24672,7 +24659,7 @@
         <v>300</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B232, $C$2:$C$748, C232, $D$2:$D$748, D232, $E$2:$E$748, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24708,7 +24695,7 @@
         <v>118</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B233, $C$2:$C$748, C233, $D$2:$D$748, D233, $E$2:$E$748, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24744,7 +24731,7 @@
         <v>117</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B234, $C$2:$C$748, C234, $D$2:$D$748, D234, $E$2:$E$748, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24790,7 +24777,7 @@
         <v>260</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B235, $C$2:$C$748, C235, $D$2:$D$748, D235, $E$2:$E$748, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="10"/>
@@ -24838,7 +24825,7 @@
         <v>500</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B236, $C$2:$C$748, C236, $D$2:$D$748, D236, $E$2:$E$748, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="41" t="s">
@@ -24887,7 +24874,7 @@
         <v>370</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B237, $C$2:$C$748, C237, $D$2:$D$748, D237, $E$2:$E$748, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P237" s="31"/>
@@ -24922,7 +24909,7 @@
       </c>
       <c r="J238" s="36"/>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B238, $C$2:$C$748, C238, $D$2:$D$748, D238, $E$2:$E$748, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24956,7 +24943,7 @@
       </c>
       <c r="J239" s="36"/>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B239, $C$2:$C$748, C239, $D$2:$D$748, D239, $E$2:$E$748, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24990,7 +24977,7 @@
       </c>
       <c r="J240" s="36"/>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B240, $C$2:$C$748, C240, $D$2:$D$748, D240, $E$2:$E$748, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25026,7 +25013,7 @@
         <v>118</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B241, $C$2:$C$748, C241, $D$2:$D$748, D241, $E$2:$E$748, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="31"/>
@@ -25063,7 +25050,7 @@
         <v>55</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B242, $C$2:$C$748, C242, $D$2:$D$748, D242, $E$2:$E$748, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25097,7 +25084,7 @@
       </c>
       <c r="J243" s="36"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B243, $C$2:$C$748, C243, $D$2:$D$748, D243, $E$2:$E$748, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25143,7 +25130,7 @@
         <v>940</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B244, $C$2:$C$748, C244, $D$2:$D$748, D244, $E$2:$E$748, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25179,7 +25166,7 @@
         <v>118</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B245, $C$2:$C$748, C245, $D$2:$D$748, D245, $E$2:$E$748, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25225,7 +25212,7 @@
         <v>285</v>
       </c>
       <c r="N246" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B246, $C$2:$C$748, C246, $D$2:$D$748, D246, $E$2:$E$748, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25271,7 +25258,7 @@
         <v>726</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B247, $C$2:$C$748, C247, $D$2:$D$748, D247, $E$2:$E$748, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25317,7 +25304,7 @@
         <v>300</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B248, $C$2:$C$748, C248, $D$2:$D$748, D248, $E$2:$E$748, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25363,7 +25350,7 @@
         <v>268</v>
       </c>
       <c r="N249" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B249, $C$2:$C$748, C249, $D$2:$D$748, D249, $E$2:$E$748, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25397,7 +25384,7 @@
       </c>
       <c r="J250" s="36"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B250, $C$2:$C$748, C250, $D$2:$D$748, D250, $E$2:$E$748, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P250" s="31"/>
@@ -25432,7 +25419,7 @@
       </c>
       <c r="J251" s="36"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B251, $C$2:$C$748, C251, $D$2:$D$748, D251, $E$2:$E$748, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25466,7 +25453,7 @@
       </c>
       <c r="J252" s="36"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B252, $C$2:$C$748, C252, $D$2:$D$748, D252, $E$2:$E$748, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25500,7 +25487,7 @@
       </c>
       <c r="J253" s="36"/>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B253, $C$2:$C$748, C253, $D$2:$D$748, D253, $E$2:$E$748, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25546,7 +25533,7 @@
         <v>300</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B254, $C$2:$C$748, C254, $D$2:$D$748, D254, $E$2:$E$748, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25585,7 +25572,7 @@
         <v>146</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B255, $C$2:$C$748, C255, $D$2:$D$748, D255, $E$2:$E$748, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25621,7 +25608,7 @@
         <v>117</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B256, $C$2:$C$748, C256, $D$2:$D$748, D256, $E$2:$E$748, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25667,7 +25654,7 @@
         <v>275</v>
       </c>
       <c r="N257" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B257, $C$2:$C$748, C257, $D$2:$D$748, D257, $E$2:$E$748, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25713,7 +25700,7 @@
         <v>250</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B258, $C$2:$C$748, C258, $D$2:$D$748, D258, $E$2:$E$748, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N298" si="13">IF(COUNTIFS( $B$2:$B$748, B258, $C$2:$C$748, C258, $D$2:$D$748, D258, $E$2:$E$748, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25747,7 +25734,7 @@
       </c>
       <c r="J259" s="36"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B259, $C$2:$C$748, C259, $D$2:$D$748, D259, $E$2:$E$748, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25793,7 +25780,7 @@
         <v>250</v>
       </c>
       <c r="N260" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B260, $C$2:$C$748, C260, $D$2:$D$748, D260, $E$2:$E$748, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25839,7 +25826,7 @@
         <v>650</v>
       </c>
       <c r="N261" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B261, $C$2:$C$748, C261, $D$2:$D$748, D261, $E$2:$E$748, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P261" s="31"/>
@@ -25874,7 +25861,7 @@
       </c>
       <c r="J262" s="36"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B262, $C$2:$C$748, C262, $D$2:$D$748, D262, $E$2:$E$748, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25908,7 +25895,7 @@
       </c>
       <c r="J263" s="36"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B263, $C$2:$C$748, C263, $D$2:$D$748, D263, $E$2:$E$748, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25954,7 +25941,7 @@
         <v>250</v>
       </c>
       <c r="N264" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B264, $C$2:$C$748, C264, $D$2:$D$748, D264, $E$2:$E$748, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P264" s="31"/>
@@ -26001,7 +25988,7 @@
         <v>480</v>
       </c>
       <c r="N265" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B265, $C$2:$C$748, C265, $D$2:$D$748, D265, $E$2:$E$748, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26047,7 +26034,7 @@
         <v>300</v>
       </c>
       <c r="N266" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B266, $C$2:$C$748, C266, $D$2:$D$748, D266, $E$2:$E$748, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26081,7 +26068,7 @@
       </c>
       <c r="J267" s="36"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B267, $C$2:$C$748, C267, $D$2:$D$748, D267, $E$2:$E$748, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26117,7 +26104,7 @@
         <v>118</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B268, $C$2:$C$748, C268, $D$2:$D$748, D268, $E$2:$E$748, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="31"/>
@@ -26154,7 +26141,7 @@
         <v>118</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B269, $C$2:$C$748, C269, $D$2:$D$748, D269, $E$2:$E$748, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26190,7 +26177,7 @@
         <v>117</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B270, $C$2:$C$748, C270, $D$2:$D$748, D270, $E$2:$E$748, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26226,7 +26213,7 @@
         <v>118</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B271, $C$2:$C$748, C271, $D$2:$D$748, D271, $E$2:$E$748, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26260,7 +26247,7 @@
       </c>
       <c r="J272" s="36"/>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B272, $C$2:$C$748, C272, $D$2:$D$748, D272, $E$2:$E$748, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26297,7 +26284,7 @@
       <c r="L273" s="18"/>
       <c r="M273" s="18"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B273, $C$2:$C$748, C273, $D$2:$D$748, D273, $E$2:$E$748, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O273" s="10"/>
@@ -26336,7 +26323,7 @@
       <c r="L274" s="18"/>
       <c r="M274" s="18"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B274, $C$2:$C$748, C274, $D$2:$D$748, D274, $E$2:$E$748, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P274" s="10"/>
@@ -26373,7 +26360,7 @@
         <v>118</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B275, $C$2:$C$748, C275, $D$2:$D$748, D275, $E$2:$E$748, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26407,7 +26394,7 @@
       </c>
       <c r="J276" s="36"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B276, $C$2:$C$748, C276, $D$2:$D$748, D276, $E$2:$E$748, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26441,7 +26428,7 @@
       </c>
       <c r="J277" s="36"/>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B277, $C$2:$C$748, C277, $D$2:$D$748, D277, $E$2:$E$748, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26477,7 +26464,7 @@
         <v>118</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B278, $C$2:$C$748, C278, $D$2:$D$748, D278, $E$2:$E$748, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26523,7 +26510,7 @@
         <v>300</v>
       </c>
       <c r="N279" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B279, $C$2:$C$748, C279, $D$2:$D$748, D279, $E$2:$E$748, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26559,7 +26546,7 @@
         <v>117</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B280, $C$2:$C$748, C280, $D$2:$D$748, D280, $E$2:$E$748, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26593,7 +26580,7 @@
       </c>
       <c r="J281" s="36"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B281, $C$2:$C$748, C281, $D$2:$D$748, D281, $E$2:$E$748, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26627,7 +26614,7 @@
       </c>
       <c r="J282" s="36"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B282, $C$2:$C$748, C282, $D$2:$D$748, D282, $E$2:$E$748, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26663,7 +26650,7 @@
         <v>118</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B283, $C$2:$C$748, C283, $D$2:$D$748, D283, $E$2:$E$748, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26699,7 +26686,7 @@
         <v>118</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B284, $C$2:$C$748, C284, $D$2:$D$748, D284, $E$2:$E$748, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26733,7 +26720,7 @@
       </c>
       <c r="J285" s="36"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B285, $C$2:$C$748, C285, $D$2:$D$748, D285, $E$2:$E$748, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="P285" s="31"/>
@@ -26773,7 +26760,7 @@
       <c r="L286" s="18"/>
       <c r="M286" s="18"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B286, $C$2:$C$748, C286, $D$2:$D$748, D286, $E$2:$E$748, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O286" s="10"/>
@@ -26811,7 +26798,7 @@
         <v>118</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B287, $C$2:$C$748, C287, $D$2:$D$748, D287, $E$2:$E$748, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26857,7 +26844,7 @@
         <v>250</v>
       </c>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B288, $C$2:$C$748, C288, $D$2:$D$748, D288, $E$2:$E$748, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26891,7 +26878,7 @@
       </c>
       <c r="J289" s="36"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B289, $C$2:$C$748, C289, $D$2:$D$748, D289, $E$2:$E$748, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26928,7 +26915,7 @@
       <c r="L290" s="18"/>
       <c r="M290" s="18"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B290, $C$2:$C$748, C290, $D$2:$D$748, D290, $E$2:$E$748, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O290" s="10"/>
@@ -26964,7 +26951,7 @@
       </c>
       <c r="J291" s="36"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B291, $C$2:$C$748, C291, $D$2:$D$748, D291, $E$2:$E$748, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26998,7 +26985,7 @@
       </c>
       <c r="J292" s="36"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B292, $C$2:$C$748, C292, $D$2:$D$748, D292, $E$2:$E$748, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O292" s="31"/>
@@ -27033,7 +27020,7 @@
       </c>
       <c r="J293" s="36"/>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B293, $C$2:$C$748, C293, $D$2:$D$748, D293, $E$2:$E$748, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27070,7 +27057,7 @@
       <c r="L294" s="17"/>
       <c r="M294" s="17"/>
       <c r="N294" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B294, $C$2:$C$748, C294, $D$2:$D$748, D294, $E$2:$E$748, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O294"/>
@@ -27109,7 +27096,7 @@
       <c r="L295" s="17"/>
       <c r="M295" s="17"/>
       <c r="N295" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B295, $C$2:$C$748, C295, $D$2:$D$748, D295, $E$2:$E$748, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
       <c r="O295"/>
@@ -27135,7 +27122,7 @@
         <v>5</v>
       </c>
       <c r="N296" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B296, $C$2:$C$748, C296, $D$2:$D$748, D296, $E$2:$E$748, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27170,7 +27157,7 @@
         <v>300</v>
       </c>
       <c r="N297" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B297, $C$2:$C$748, C297, $D$2:$D$748, D297, $E$2:$E$748, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -27205,7 +27192,7 @@
         <v>720</v>
       </c>
       <c r="N298" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$748, B298, $C$2:$C$748, C298, $D$2:$D$748, D298, $E$2:$E$748, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="13"/>
         <v>Unique</v>
       </c>
     </row>

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_17sep26_Thurs.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_17sep26_Thurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89F6FE4-9B10-427E-B1A7-45524D9F4232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979E47D4-E083-40C9-8847-2C76CA9CFA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3026,7 +3026,7 @@
       <c r="O36"/>
       <c r="P36" s="10"/>
     </row>
-    <row r="37" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
@@ -4887,7 +4887,9 @@
         <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
-      <c r="O79" s="10"/>
+      <c r="O79" s="41" t="s">
+        <v>247</v>
+      </c>
       <c r="P79" s="10"/>
     </row>
     <row r="80" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5074,7 +5076,6 @@
         <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
-      <c r="O83" s="54"/>
       <c r="P83" s="31"/>
     </row>
     <row r="84" spans="1:16" s="19" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5122,7 +5123,7 @@
         <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
-      <c r="O84" s="54"/>
+      <c r="O84" s="10"/>
       <c r="P84" s="31"/>
     </row>
     <row r="85" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6045,7 +6046,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46281.375</v>
       </c>
@@ -6090,6 +6091,9 @@
         <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
+      <c r="O105" s="41" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="106" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
@@ -6331,7 +6335,9 @@
         <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
-      <c r="O110" s="31"/>
+      <c r="O110" s="41" t="s">
+        <v>247</v>
+      </c>
       <c r="P110" s="31"/>
     </row>
     <row r="111" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6379,7 +6385,9 @@
         <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
-      <c r="O111" s="31"/>
+      <c r="O111" s="41" t="s">
+        <v>247</v>
+      </c>
       <c r="P111" s="31"/>
     </row>
     <row r="112" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6815,9 +6823,7 @@
         <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
-      <c r="O121" s="41" t="s">
-        <v>247</v>
-      </c>
+      <c r="O121" s="54"/>
     </row>
     <row r="122" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="32">
@@ -6864,9 +6870,7 @@
         <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
-      <c r="O122" s="41" t="s">
-        <v>247</v>
-      </c>
+      <c r="O122" s="54"/>
     </row>
     <row r="123" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
@@ -7459,6 +7463,9 @@
         <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
+      <c r="O135" s="41" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="136" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3">
@@ -7551,9 +7558,7 @@
         <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
-      <c r="O137" s="41" t="s">
-        <v>247</v>
-      </c>
+      <c r="O137" s="54"/>
     </row>
     <row r="138" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3">
@@ -8301,9 +8306,7 @@
         <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
-      <c r="O153" s="41" t="s">
-        <v>247</v>
-      </c>
+      <c r="O153" s="54"/>
       <c r="P153"/>
     </row>
     <row r="154" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8963,7 +8966,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="169" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -9810,7 +9813,7 @@
       </c>
       <c r="O187" s="31"/>
     </row>
-    <row r="188" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -9855,9 +9858,7 @@
         <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
-      <c r="O188" s="41" t="s">
-        <v>247</v>
-      </c>
+      <c r="O188" s="54"/>
       <c r="P188" s="31"/>
     </row>
     <row r="189" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10846,7 +10847,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="212" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -11820,7 +11821,7 @@
       <c r="O235" s="10"/>
       <c r="P235" s="10"/>
     </row>
-    <row r="236" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="3">
         <v>46268.375</v>
       </c>
@@ -12115,7 +12116,7 @@
       </c>
       <c r="O242" s="31"/>
     </row>
-    <row r="243" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3">
         <v>46261.375</v>
       </c>
@@ -12779,7 +12780,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="260" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -12825,7 +12826,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="261" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="3">
         <v>46266.375</v>
       </c>
@@ -13056,7 +13057,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="267" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -13412,7 +13413,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="276" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -14228,7 +14229,7 @@
   <autoFilter ref="A1:P297" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="ARE&amp;MEQ"/>
+        <filter val="ZENTECEQ"/>
       </filters>
     </filterColumn>
   </autoFilter>
